--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44860</v>
+        <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,49 +1421,53 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,17 +1497,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1517,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1533,42 +1537,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1586,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1601,14 +1605,14 @@
         <v>6.4</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1622,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1638,42 +1642,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46064</v>
+        <v>44860</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,16 +1707,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>12.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1727,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1736,49 +1740,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,16 +1812,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1832,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,42 +1852,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1953,35 +1957,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
@@ -2005,7 +2009,7 @@
         <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2093,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2107,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>45222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2123,7 +2127,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2132,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2147,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2163,39 +2167,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45196</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45117</v>
+        <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45126</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3995,13 +3995,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4044,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4058,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45566</v>
+        <v>45306</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4074,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4117,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4131,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44911</v>
+        <v>45233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4146,13 +4141,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4195,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4209,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45110</v>
+        <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4225,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4268,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4282,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46071</v>
+        <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4298,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4341,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4355,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46071</v>
+        <v>45866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4371,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4414,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4428,10 +4418,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45299</v>
+        <v>45148</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4444,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4487,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45817</v>
+        <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4517,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>12.7</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4560,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45629</v>
+        <v>45235</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4590,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4633,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,10 +4637,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45674</v>
+        <v>45000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4663,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4710,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45833</v>
+        <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45674</v>
+        <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45033</v>
+        <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45728</v>
+        <v>46071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4955,7 +4945,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45174</v>
+        <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5018,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45148</v>
+        <v>45817</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45217</v>
+        <v>45833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5164,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5207,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5221,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45110</v>
+        <v>45728</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5237,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5290,7 +5280,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5300,14 +5290,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45195</v>
+        <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5320,7 +5310,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5363,7 +5353,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5377,10 +5367,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45243</v>
+        <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5393,7 +5383,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5436,7 +5426,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5450,10 +5440,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45110</v>
+        <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5466,7 +5456,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5509,7 +5499,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5523,10 +5513,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45972</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5539,7 +5529,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5582,7 +5572,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5596,10 +5586,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45180</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5612,7 +5602,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5655,7 +5645,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5669,10 +5659,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45068</v>
+        <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5685,7 +5675,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5718,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5738,14 +5728,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45551</v>
+        <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5758,7 +5748,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5791,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5815,10 +5805,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45993</v>
+        <v>45126</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5836,7 +5826,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5879,7 +5869,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5893,10 +5883,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45996</v>
+        <v>45148</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5909,7 +5899,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5952,7 +5942,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5966,10 +5956,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5981,8 +5971,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6025,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45180</v>
+        <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46136</v>
+        <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6185,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45235</v>
+        <v>46136</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45947</v>
+        <v>45033</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>45104</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44831</v>
+        <v>45384</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45512</v>
+        <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45866</v>
+        <v>45889</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45148</v>
+        <v>45937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6634,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46064</v>
+        <v>46170</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6707,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6750,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44824</v>
+        <v>46184</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6780,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6823,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6837,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45148</v>
+        <v>46183</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6853,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>15.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6896,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6910,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45889</v>
+        <v>46195</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6926,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6969,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6983,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45233</v>
+        <v>45300</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +6999,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7042,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7056,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>46230</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7072,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7115,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7129,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45174</v>
+        <v>46230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7145,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7188,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7202,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46170</v>
+        <v>44911</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7222,8 +7217,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45306</v>
+        <v>44804</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44804</v>
+        <v>45566</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46183</v>
+        <v>45299</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>15.6</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46184</v>
+        <v>45243</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46195</v>
+        <v>44993</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44993</v>
+        <v>45217</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45000</v>
+        <v>45196</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44494</v>
+        <v>45566</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45357</v>
+        <v>45148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45127</v>
+        <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45415</v>
+        <v>45117</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45384</v>
+        <v>45127</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45208</v>
+        <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45566</v>
+        <v>45208</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46230</v>
+        <v>45110</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46230</v>
+        <v>45180</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45104</v>
+        <v>45357</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45300</v>
+        <v>45174</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45622</v>
+        <v>45415</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45491</v>
+        <v>45195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45300</v>
+        <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45328</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45440</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45315</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45106</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>44837</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45230</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45770</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>46127</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46147</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45798</v>
+        <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>12.8</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,53 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1481,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46064</v>
+        <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1497,16 +1493,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1521,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1537,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1586,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46120</v>
+        <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1605,13 +1601,13 @@
         <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1626,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1642,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44860</v>
+        <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1707,17 +1703,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1731,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1740,42 +1736,42 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1795,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1883,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1897,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,17 +1913,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1941,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1957,35 +1953,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2005,7 @@
         <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2093,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2107,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45222</v>
+        <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2123,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2136,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2151,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2167,35 +2163,39 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44509</v>
+        <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44833</v>
+        <v>45196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45068</v>
+        <v>45306</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45551</v>
+        <v>44804</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>45365</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45306</v>
+        <v>45833</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45233</v>
+        <v>44862</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44831</v>
+        <v>45126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4214,8 +4214,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4263,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4277,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45300</v>
+        <v>45566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4288,7 +4293,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4336,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45866</v>
+        <v>44911</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4360,8 +4365,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4414,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4428,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4444,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4487,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4501,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45110</v>
+        <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4517,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4560,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4574,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45235</v>
+        <v>45947</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4590,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45000</v>
+        <v>45728</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4663,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4706,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4710,10 +4720,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45674</v>
+        <v>45512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4736,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4779,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4793,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46064</v>
+        <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4809,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4852,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4866,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46071</v>
+        <v>45299</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4925,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46071</v>
+        <v>45972</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4955,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4998,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45629</v>
+        <v>45674</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45817</v>
+        <v>45674</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5101,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5144,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45833</v>
+        <v>45033</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5164,7 +5174,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5207,7 +5217,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5221,10 +5231,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45728</v>
+        <v>45993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5236,8 +5246,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5280,7 +5295,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5294,10 +5309,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44824</v>
+        <v>45996</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5310,7 +5325,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5353,7 +5368,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5367,10 +5382,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45180</v>
+        <v>45174</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5383,7 +5398,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5426,7 +5441,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5440,10 +5455,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45512</v>
+        <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5456,7 +5471,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5499,7 +5514,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5513,10 +5528,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5587,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5586,10 +5601,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45972</v>
+        <v>45217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5602,7 +5617,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5645,7 +5660,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5659,10 +5674,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45947</v>
+        <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5675,7 +5690,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5718,7 +5733,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5728,14 +5743,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44862</v>
+        <v>45195</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5748,7 +5763,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5791,7 +5806,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5805,10 +5820,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45126</v>
+        <v>45243</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5820,13 +5835,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5869,7 +5879,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5883,10 +5893,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5899,7 +5909,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5942,7 +5952,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5956,10 +5966,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45993</v>
+        <v>45866</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5971,13 +5981,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6025,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45996</v>
+        <v>45889</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6098,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45996</v>
+        <v>45180</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6171,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6185,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46136</v>
+        <v>45068</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6201,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45033</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6312,7 +6317,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6322,14 +6327,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45104</v>
+        <v>45551</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6347,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45384</v>
+        <v>46170</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45622</v>
+        <v>45180</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45889</v>
+        <v>45235</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45937</v>
+        <v>45000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6634,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6677,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46170</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6707,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>13.5</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6750,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6764,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46184</v>
+        <v>44831</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6780,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6840,7 +6845,7 @@
         <v>46183</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6896,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6910,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46195</v>
+        <v>46064</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6926,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6969,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6983,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45300</v>
+        <v>46071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6999,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7042,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7056,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46230</v>
+        <v>46071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7072,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7115,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7129,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46230</v>
+        <v>46184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7145,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7188,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7202,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44911</v>
+        <v>44494</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7217,13 +7222,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44804</v>
+        <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45566</v>
+        <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45299</v>
+        <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45243</v>
+        <v>45127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44993</v>
+        <v>45415</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45217</v>
+        <v>44824</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45196</v>
+        <v>45148</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45566</v>
+        <v>45384</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45148</v>
+        <v>45233</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44494</v>
+        <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45117</v>
+        <v>45208</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45127</v>
+        <v>45566</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45174</v>
+        <v>45104</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45208</v>
+        <v>45300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45110</v>
+        <v>46230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45180</v>
+        <v>46230</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45357</v>
+        <v>45622</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45174</v>
+        <v>45491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45415</v>
+        <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45195</v>
+        <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>12.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45491</v>
+        <v>45629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45328</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44796</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45440</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45315</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45106</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>44837</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45230</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45770</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>46127</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46147</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE120"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44860</v>
+        <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,49 +1421,53 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,17 +1497,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1517,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1533,42 +1537,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1586,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>44860</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1602,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1631,42 +1635,42 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
@@ -1690,7 +1694,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1778,7 +1782,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,7 +1812,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1848,42 +1852,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1917,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1937,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,35 +1957,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
@@ -2005,7 +2009,7 @@
         <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2093,7 +2097,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2107,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>45222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2123,7 +2127,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2132,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2147,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2163,39 +2167,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44509</v>
+        <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45196</v>
+        <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44833</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45306</v>
+        <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44804</v>
+        <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45365</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45117</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45833</v>
+        <v>45306</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44862</v>
+        <v>45233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45126</v>
+        <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4214,13 +4214,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4263,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4277,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45566</v>
+        <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4336,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44911</v>
+        <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4365,13 +4360,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4414,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4431,7 +4421,7 @@
         <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4444,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4487,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46136</v>
+        <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4517,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4560,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45947</v>
+        <v>45000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4590,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4633,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,10 +4637,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45728</v>
+        <v>45674</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4663,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4710,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45512</v>
+        <v>44824</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44993</v>
+        <v>45180</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45299</v>
+        <v>45629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45972</v>
+        <v>45817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4955,7 +4945,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>12.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45674</v>
+        <v>45728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5018,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45674</v>
+        <v>46064</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45033</v>
+        <v>45365</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5164,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5207,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5221,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45993</v>
+        <v>45972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5246,13 +5236,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5295,7 +5280,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5309,10 +5294,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45996</v>
+        <v>44862</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5325,7 +5310,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5368,7 +5353,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5382,10 +5367,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45174</v>
+        <v>46071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5398,7 +5383,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5441,7 +5426,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5455,10 +5440,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45996</v>
+        <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5471,7 +5456,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5514,7 +5499,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5528,10 +5513,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45148</v>
+        <v>45126</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5543,8 +5528,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5587,7 +5577,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5601,10 +5591,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45217</v>
+        <v>45148</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5617,7 +5607,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5660,7 +5650,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5674,10 +5664,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45110</v>
+        <v>45993</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5689,8 +5679,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5733,7 +5728,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5743,14 +5738,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45195</v>
+        <v>45833</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5763,7 +5758,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5806,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5820,10 +5815,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45243</v>
+        <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5836,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45996</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5909,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5952,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45866</v>
+        <v>45033</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5982,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6025,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45889</v>
+        <v>45866</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45180</v>
+        <v>45104</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6185,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45068</v>
+        <v>45384</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45937</v>
+        <v>45622</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6327,14 +6322,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45551</v>
+        <v>45300</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46170</v>
+        <v>45512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>13.5</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45180</v>
+        <v>45947</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45235</v>
+        <v>46136</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45000</v>
+        <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6638,8 +6633,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45110</v>
+        <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44831</v>
+        <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46183</v>
+        <v>45937</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>15.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46064</v>
+        <v>46170</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>13.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46071</v>
+        <v>45566</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46071</v>
+        <v>45299</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46184</v>
+        <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44494</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45148</v>
+        <v>46183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>15.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46195</v>
+        <v>44993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45357</v>
+        <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45127</v>
+        <v>45196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45415</v>
+        <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44824</v>
+        <v>45566</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7721,7 +7721,7 @@
         <v>45148</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45384</v>
+        <v>44494</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45233</v>
+        <v>45117</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45174</v>
+        <v>45127</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45208</v>
+        <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45566</v>
+        <v>45208</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45104</v>
+        <v>45110</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45300</v>
+        <v>46230</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8305,7 +8305,7 @@
         <v>46230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46230</v>
+        <v>45180</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45622</v>
+        <v>45357</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45491</v>
+        <v>45174</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>45415</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45817</v>
+        <v>45195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45629</v>
+        <v>46281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,24 +8799,24 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S 177-2025</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45677</v>
+        <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8872,7 +8872,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S 336-2024</t>
+          <t>S 177-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45328</v>
+        <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>25.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 181-2025</t>
+          <t>S 336-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45677</v>
+        <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>12.8</v>
+        <v>25.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 4689-2022</t>
+          <t>S 181-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44796</v>
+        <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>34</v>
+        <v>12.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9091,7 +9091,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 1864-2024</t>
+          <t>S 4689-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45440</v>
+        <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 180-2025</t>
+          <t>S 1864-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45677</v>
+        <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>11.6</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 205-2024</t>
+          <t>S 180-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45315</v>
+        <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 2344-2023</t>
+          <t>S 205-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45106</v>
+        <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>29.9</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 2345-2023</t>
+          <t>S 2344-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>31.6</v>
+        <v>29.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 5531-2022</t>
+          <t>S 2345-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44837</v>
+        <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.3</v>
+        <v>31.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 2350-2023</t>
+          <t>S 5531-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45106</v>
+        <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>22.7</v>
+        <v>5.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9602,7 +9602,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 3886-2023</t>
+          <t>S 2350-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45230</v>
+        <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.9</v>
+        <v>22.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 1330-2025</t>
+          <t>S 3886-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45770</v>
+        <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>12.7</v>
+        <v>4.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9748,7 +9748,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 1065-2026</t>
+          <t>S 1330-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46127</v>
+        <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 1381-2026</t>
+          <t>S 1065-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46147</v>
+        <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9894,7 +9894,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 1379-2026</t>
+          <t>S 1381-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9967,148 +9967,221 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
+          <t>S 1379-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>S 1315-2026</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D119" s="1" t="n">
+      <c r="D120" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="E119" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
+      <c r="E120" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
         <v>2.6</v>
       </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>S 1377-2026</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D120" s="1" t="n">
+      <c r="D121" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="E120" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
+      <c r="E121" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
         <v>7</v>
       </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" s="2" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45798</v>
+        <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>12.8</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,53 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1481,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46064</v>
+        <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1497,16 +1493,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1521,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1537,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1586,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44860</v>
+        <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1602,13 +1598,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1635,49 +1631,49 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46120</v>
+        <v>46064</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1707,7 +1703,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1747,42 +1743,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,10 +1792,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45414</v>
+        <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1812,17 +1808,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1836,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1852,35 +1848,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1900,7 @@
         <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2005,7 @@
         <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2093,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2107,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45222</v>
+        <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,7 +2123,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2136,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2151,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2167,35 +2163,39 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45551</v>
+        <v>45117</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>45126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3995,8 +3995,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4044,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4058,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45306</v>
+        <v>45566</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4074,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4117,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4131,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45233</v>
+        <v>44911</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4141,8 +4146,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4195,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4209,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44831</v>
+        <v>46071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4225,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4268,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4282,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45300</v>
+        <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4288,7 +4298,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4341,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4355,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4371,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4414,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4428,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45110</v>
+        <v>45833</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4444,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4487,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4501,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45235</v>
+        <v>45299</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4517,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4560,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4574,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45000</v>
+        <v>45817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4590,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>12.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45674</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4663,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4706,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4710,10 +4720,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44824</v>
+        <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4736,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4779,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4793,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45180</v>
+        <v>45674</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4809,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4852,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4866,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45629</v>
+        <v>45033</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4925,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45817</v>
+        <v>46136</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4955,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4998,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45728</v>
+        <v>45947</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46064</v>
+        <v>45174</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5101,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5144,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45365</v>
+        <v>45148</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5217,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5221,10 +5231,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45972</v>
+        <v>45217</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5237,7 +5247,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5280,7 +5290,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5294,10 +5304,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44862</v>
+        <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5310,7 +5320,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5353,7 +5363,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5367,10 +5377,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46071</v>
+        <v>45110</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5383,7 +5393,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5426,7 +5436,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5436,14 +5446,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46071</v>
+        <v>45195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5456,7 +5466,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5499,7 +5509,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5513,10 +5523,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45126</v>
+        <v>45243</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5528,13 +5538,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5577,7 +5582,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5591,10 +5596,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5612,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5650,7 +5655,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45993</v>
+        <v>45180</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5679,13 +5684,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45833</v>
+        <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45996</v>
+        <v>45551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45996</v>
+        <v>45180</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45033</v>
+        <v>45235</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45866</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45104</v>
+        <v>44831</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45384</v>
+        <v>45889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45622</v>
+        <v>45148</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45300</v>
+        <v>45937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45512</v>
+        <v>45728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45947</v>
+        <v>46170</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>15.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44911</v>
+        <v>46184</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6633,13 +6633,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44804</v>
+        <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6707,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6750,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45889</v>
+        <v>45148</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6780,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6823,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6837,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45937</v>
+        <v>46195</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6853,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6896,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6910,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46170</v>
+        <v>45972</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6926,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.5</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6969,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6983,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45566</v>
+        <v>45233</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +6999,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7042,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7056,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45299</v>
+        <v>45174</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7072,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7115,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7129,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45243</v>
+        <v>45306</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7145,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7188,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7202,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>44804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7218,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7261,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7275,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46183</v>
+        <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7295,8 +7290,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>15.6</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44993</v>
+        <v>45996</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45217</v>
+        <v>45996</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45196</v>
+        <v>45866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45566</v>
+        <v>46230</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45148</v>
+        <v>44993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44494</v>
+        <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45117</v>
+        <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45127</v>
+        <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45174</v>
+        <v>46064</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45208</v>
+        <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45110</v>
+        <v>45127</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46230</v>
+        <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46230</v>
+        <v>45384</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45180</v>
+        <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45357</v>
+        <v>45566</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45174</v>
+        <v>45104</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45415</v>
+        <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45195</v>
+        <v>45622</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46281</v>
+        <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45491</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>45854</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1533,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1638,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46064</v>
+        <v>45056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1739,46 +1739,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46120</v>
+        <v>45222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1811,13 +1811,13 @@
         <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1848,42 +1848,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45854</v>
+        <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,17 +1913,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,42 +1953,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45056</v>
+        <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2054,39 +2054,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
         <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45196</v>
+        <v>45068</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45365</v>
+        <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45117</v>
+        <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45126</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3995,13 +3995,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4044,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4058,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45566</v>
+        <v>45306</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4074,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4117,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4131,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44911</v>
+        <v>45233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4146,13 +4141,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4195,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4209,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46071</v>
+        <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4225,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4268,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4282,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46071</v>
+        <v>45148</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4298,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4341,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4358,7 +4348,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4371,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4414,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4428,10 +4418,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45833</v>
+        <v>45235</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4487,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45299</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4517,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4560,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45817</v>
+        <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4590,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>12.7</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4633,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,10 +4637,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45629</v>
+        <v>44824</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4663,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4710,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45674</v>
+        <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45674</v>
+        <v>45365</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45033</v>
+        <v>44862</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46136</v>
+        <v>45126</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4954,8 +4944,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +4993,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45947</v>
+        <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5023,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5066,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5080,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45174</v>
+        <v>45033</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5096,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5139,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5153,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45148</v>
+        <v>46136</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5169,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5212,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5226,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45217</v>
+        <v>45104</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5242,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5290,7 +5285,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5304,10 +5299,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45512</v>
+        <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5320,7 +5315,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5363,7 +5358,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5377,10 +5372,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45110</v>
+        <v>45622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5393,7 +5388,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5436,7 +5431,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5446,14 +5441,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45195</v>
+        <v>45728</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5466,7 +5461,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5509,7 +5504,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5523,10 +5518,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45243</v>
+        <v>45300</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5539,7 +5534,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5582,7 +5577,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5596,10 +5591,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5612,7 +5607,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45180</v>
+        <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5685,7 +5680,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5723,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,10 +5737,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45068</v>
+        <v>45993</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5757,8 +5752,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45551</v>
+        <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5888,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45180</v>
+        <v>45996</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45235</v>
+        <v>45866</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>44911</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6049,8 +6049,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6098,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44831</v>
+        <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6171,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6185,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45889</v>
+        <v>46170</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6201,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45148</v>
+        <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,7 +6274,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6317,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45937</v>
+        <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6347,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45728</v>
+        <v>46064</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46170</v>
+        <v>45299</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13.5</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46183</v>
+        <v>46071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.6</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46184</v>
+        <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6634,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6677,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44824</v>
+        <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6707,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6750,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6764,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45148</v>
+        <v>46183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6780,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>15.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6823,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6837,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6853,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6896,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6910,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45972</v>
+        <v>45243</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6926,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6969,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6983,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45233</v>
+        <v>44993</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6999,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7042,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7056,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45174</v>
+        <v>45217</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7072,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7115,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7129,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45306</v>
+        <v>45196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7145,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7188,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7202,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44804</v>
+        <v>46195</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7218,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7261,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7275,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45993</v>
+        <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7290,13 +7295,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45996</v>
+        <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45996</v>
+        <v>45512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45866</v>
+        <v>45947</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46230</v>
+        <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46230</v>
+        <v>45117</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44993</v>
+        <v>45127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46281</v>
+        <v>45174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45000</v>
+        <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44494</v>
+        <v>45110</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46064</v>
+        <v>45180</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8086,7 +8086,7 @@
         <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45127</v>
+        <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8232,7 +8232,7 @@
         <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8298,14 +8298,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45384</v>
+        <v>45195</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45208</v>
+        <v>46230</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45566</v>
+        <v>46230</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45104</v>
+        <v>45491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45622</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45491</v>
+        <v>45629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>45817</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>12.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45854</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45068</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45306</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45148</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45235</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44824</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45365</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44862</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45126</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45033</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>46136</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45104</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45384</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45728</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>45300</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45993</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45996</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45866</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44911</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46170</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>46064</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45299</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>46071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>46184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45243</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44993</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>45217</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>46195</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45947</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45117</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>45127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45110</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45180</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45195</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>46230</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>46230</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45817</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45854</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45056</v>
+        <v>46064</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1739,46 +1739,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45222</v>
+        <v>45056</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,17 +1808,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1844,46 +1844,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46064</v>
+        <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,35 +1953,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
         <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45068</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45674</v>
+        <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
         <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45306</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45233</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45148</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45110</v>
+        <v>45000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45235</v>
+        <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>45674</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45674</v>
+        <v>45235</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
         <v>44824</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45365</v>
+        <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44862</v>
+        <v>45817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>12.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45126</v>
+        <v>45947</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4944,13 +4944,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4993,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5007,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45148</v>
+        <v>45365</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5066,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5080,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45033</v>
+        <v>44862</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5096,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5139,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5153,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46136</v>
+        <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5168,8 +5163,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45104</v>
+        <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5285,7 +5285,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45384</v>
+        <v>46136</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45622</v>
+        <v>45033</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45728</v>
+        <v>45104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45300</v>
+        <v>45384</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45972</v>
+        <v>45728</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>45889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45993</v>
+        <v>45622</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5752,13 +5752,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5796,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5815,10 +5810,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45996</v>
+        <v>45972</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5826,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5869,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45996</v>
+        <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5904,7 +5899,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5942,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5956,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45866</v>
+        <v>46170</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5972,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>13.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6015,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6029,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44911</v>
+        <v>45993</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45937</v>
+        <v>45300</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6185,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46170</v>
+        <v>45996</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13.5</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44804</v>
+        <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45566</v>
+        <v>45866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46064</v>
+        <v>46184</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45299</v>
+        <v>46183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>15.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46071</v>
+        <v>46195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6634,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46184</v>
+        <v>46071</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6707,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6750,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46183</v>
+        <v>46071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6780,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>15.6</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6823,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6837,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45833</v>
+        <v>44911</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6857,8 +6852,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45243</v>
+        <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44993</v>
+        <v>44804</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45217</v>
+        <v>45566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45196</v>
+        <v>45512</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46195</v>
+        <v>45299</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45566</v>
+        <v>45243</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45148</v>
+        <v>44993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45512</v>
+        <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45947</v>
+        <v>45196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44494</v>
+        <v>45566</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45117</v>
+        <v>45148</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45127</v>
+        <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45174</v>
+        <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45208</v>
+        <v>44494</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45180</v>
+        <v>45127</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45357</v>
+        <v>45174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45174</v>
+        <v>45208</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45415</v>
+        <v>46281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8298,14 +8298,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45195</v>
+        <v>45110</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46230</v>
+        <v>45180</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46230</v>
+        <v>45357</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45491</v>
+        <v>45174</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46281</v>
+        <v>45415</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45300</v>
+        <v>45195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45629</v>
+        <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45817</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12.7</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1533,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45414</v>
+        <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1638,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46064</v>
+        <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1743,42 +1743,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45056</v>
+        <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,7 +1812,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1844,46 +1848,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1916,14 +1920,14 @@
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1937,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,16 +2022,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2042,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2058,42 +2062,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2107,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2159,43 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44833</v>
+        <v>45674</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44596</v>
+        <v>45033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44596</v>
+        <v>45491</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45068</v>
+        <v>45174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45551</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3983,7 +3983,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4049,14 +4049,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45306</v>
+        <v>45195</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45233</v>
+        <v>44596</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44831</v>
+        <v>45243</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45148</v>
+        <v>44596</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45000</v>
+        <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4421,7 +4421,7 @@
         <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45674</v>
+        <v>45180</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45235</v>
+        <v>45068</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44824</v>
+        <v>45551</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4713,7 +4713,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45629</v>
+        <v>45235</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45817</v>
+        <v>45110</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>12.7</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45947</v>
+        <v>45365</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45365</v>
+        <v>44831</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44862</v>
+        <v>45117</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45126</v>
+        <v>45148</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5163,13 +5163,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5212,7 +5207,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5226,10 +5221,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45148</v>
+        <v>44862</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5242,7 +5237,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5285,7 +5280,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5299,10 +5294,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46136</v>
+        <v>45300</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5315,7 +5310,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5358,7 +5353,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5372,10 +5367,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45033</v>
+        <v>45126</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5387,8 +5382,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45104</v>
+        <v>45566</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45384</v>
+        <v>44824</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>45728</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45889</v>
+        <v>44911</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5679,8 +5679,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5723,7 +5728,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5737,10 +5742,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45622</v>
+        <v>45110</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5753,7 +5758,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5796,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5810,10 +5815,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45972</v>
+        <v>45148</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5826,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5869,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5883,10 +5888,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45937</v>
+        <v>45233</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5899,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5942,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5956,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46170</v>
+        <v>45972</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5972,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>13.5</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6015,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6029,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45993</v>
+        <v>45299</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6044,13 +6049,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45300</v>
+        <v>45174</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45996</v>
+        <v>45674</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6268,8 +6268,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6317,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45866</v>
+        <v>45996</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6347,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46184</v>
+        <v>45306</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46183</v>
+        <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>15.6</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46195</v>
+        <v>44804</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46064</v>
+        <v>45866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6634,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6677,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6707,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6750,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6767,7 +6772,7 @@
         <v>46071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6823,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6837,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44911</v>
+        <v>46071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6852,13 +6857,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45833</v>
+        <v>44993</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44804</v>
+        <v>45833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45566</v>
+        <v>45000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45512</v>
+        <v>44494</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45299</v>
+        <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>12.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45243</v>
+        <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44993</v>
+        <v>45357</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45217</v>
+        <v>45127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45196</v>
+        <v>46136</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45566</v>
+        <v>45947</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45148</v>
+        <v>45415</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46230</v>
+        <v>45512</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46230</v>
+        <v>45384</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44494</v>
+        <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45117</v>
+        <v>45566</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45127</v>
+        <v>45104</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45174</v>
+        <v>45300</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45208</v>
+        <v>45622</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46281</v>
+        <v>45889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45110</v>
+        <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45180</v>
+        <v>46170</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>13.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45357</v>
+        <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>15.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45174</v>
+        <v>46184</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45415</v>
+        <v>46195</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45195</v>
+        <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45491</v>
+        <v>46230</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>45854</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1533,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1638,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45798</v>
+        <v>45056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1739,43 +1739,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1795,7 @@
         <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1883,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1897,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46120</v>
+        <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1920,13 +1916,13 @@
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1941,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1957,42 +1953,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2002,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854</v>
+        <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,17 +2018,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2046,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2062,42 +2058,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2107,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45056</v>
+        <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2163,39 +2159,43 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45674</v>
+        <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45033</v>
+        <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45491</v>
+        <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44833</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45174</v>
+        <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45217</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3983,7 +3983,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4049,14 +4049,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45195</v>
+        <v>45233</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44596</v>
+        <v>44831</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45243</v>
+        <v>45306</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44596</v>
+        <v>45148</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45196</v>
+        <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45110</v>
+        <v>45235</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45180</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45068</v>
+        <v>45674</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45551</v>
+        <v>44824</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4713,7 +4713,7 @@
         <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45235</v>
+        <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45110</v>
+        <v>45817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>12.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45365</v>
+        <v>45947</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44831</v>
+        <v>45365</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45117</v>
+        <v>44862</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45148</v>
+        <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5163,8 +5163,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5207,7 +5212,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5221,10 +5226,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44862</v>
+        <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5237,7 +5242,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5280,7 +5285,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5294,10 +5299,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45300</v>
+        <v>45033</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5310,7 +5315,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5353,7 +5358,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5367,10 +5372,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45126</v>
+        <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5382,13 +5387,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45566</v>
+        <v>45384</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44824</v>
+        <v>45728</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45728</v>
+        <v>45622</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44911</v>
+        <v>46136</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5679,13 +5679,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5723,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,10 +5737,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45110</v>
+        <v>45972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5758,7 +5753,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5796,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5815,10 +5810,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45148</v>
+        <v>45300</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5826,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5869,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45233</v>
+        <v>45993</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5903,8 +5898,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45972</v>
+        <v>45996</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45299</v>
+        <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45174</v>
+        <v>45866</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45674</v>
+        <v>45889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45993</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,11 +6266,6 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45996</v>
+        <v>44911</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6346,8 +6341,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45306</v>
+        <v>46170</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>13.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45996</v>
+        <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44804</v>
+        <v>46071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45866</v>
+        <v>46071</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46064</v>
+        <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46071</v>
+        <v>45833</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46071</v>
+        <v>46184</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44993</v>
+        <v>46183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>15.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45833</v>
+        <v>45566</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45000</v>
+        <v>45299</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44494</v>
+        <v>45243</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45817</v>
+        <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>12.7</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45629</v>
+        <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45357</v>
+        <v>44993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45127</v>
+        <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46136</v>
+        <v>45196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45947</v>
+        <v>45566</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45415</v>
+        <v>45148</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45512</v>
+        <v>44494</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45384</v>
+        <v>45117</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45208</v>
+        <v>45127</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45566</v>
+        <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45104</v>
+        <v>45208</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45300</v>
+        <v>46230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45622</v>
+        <v>45110</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45889</v>
+        <v>46230</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45937</v>
+        <v>45180</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46170</v>
+        <v>45357</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>13.5</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46183</v>
+        <v>45174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>15.6</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46184</v>
+        <v>46281</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46195</v>
+        <v>45415</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46230</v>
+        <v>45195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46230</v>
+        <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46281</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1533,42 +1533,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45414</v>
+        <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1638,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45056</v>
+        <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1739,39 +1739,43 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -1795,7 +1799,7 @@
         <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1883,7 +1887,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1916,14 +1920,14 @@
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1937,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,16 +2022,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2042,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2058,42 +2062,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2107,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2159,43 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45551</v>
+        <v>45866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45233</v>
+        <v>45126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4068,8 +4068,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4117,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4131,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44831</v>
+        <v>45566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4147,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4190,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4204,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45306</v>
+        <v>46064</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4220,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4263,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4277,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45148</v>
+        <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4288,7 +4293,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4336,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4350,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45110</v>
+        <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4366,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4409,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4423,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45235</v>
+        <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4482,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>44911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4506,8 +4511,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4560,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4574,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45674</v>
+        <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4590,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44824</v>
+        <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4663,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4706,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4710,10 +4720,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45180</v>
+        <v>45728</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4736,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4779,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4793,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45629</v>
+        <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4809,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4852,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4866,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45817</v>
+        <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>12.7</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4925,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45947</v>
+        <v>45674</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4955,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4998,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45365</v>
+        <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44862</v>
+        <v>45947</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5101,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5144,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45126</v>
+        <v>45674</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5163,13 +5173,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5212,7 +5217,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5226,10 +5231,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45148</v>
+        <v>45033</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5242,7 +5247,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5285,7 +5290,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5299,10 +5304,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45033</v>
+        <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5315,7 +5320,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5358,7 +5363,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5372,10 +5377,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45104</v>
+        <v>45993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5387,8 +5392,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5431,7 +5441,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5445,10 +5455,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45384</v>
+        <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5471,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5504,7 +5514,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5518,10 +5528,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45728</v>
+        <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5544,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5577,7 +5587,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5591,10 +5601,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45622</v>
+        <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5617,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5650,7 +5660,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5664,10 +5674,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46136</v>
+        <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5680,7 +5690,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5723,7 +5733,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5737,10 +5747,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45972</v>
+        <v>45217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5753,7 +5763,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5796,7 +5806,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5810,10 +5820,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45300</v>
+        <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5826,7 +5836,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5869,7 +5879,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5879,14 +5889,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45993</v>
+        <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5898,13 +5908,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5952,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5966,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45996</v>
+        <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5982,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6025,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45996</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6098,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45866</v>
+        <v>45180</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6171,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6185,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45889</v>
+        <v>45068</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6201,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6249,14 +6254,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45937</v>
+        <v>45551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,7 +6274,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6317,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44911</v>
+        <v>45180</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6341,13 +6346,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46170</v>
+        <v>45235</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46064</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46071</v>
+        <v>44831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46071</v>
+        <v>45889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44804</v>
+        <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45833</v>
+        <v>46170</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46184</v>
+        <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>46183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45566</v>
+        <v>45817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>12.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45299</v>
+        <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45243</v>
+        <v>46184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45512</v>
+        <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44993</v>
+        <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45217</v>
+        <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45196</v>
+        <v>45174</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45566</v>
+        <v>45306</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45148</v>
+        <v>44804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44494</v>
+        <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45117</v>
+        <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45127</v>
+        <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45174</v>
+        <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45208</v>
+        <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46230</v>
+        <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45110</v>
+        <v>45357</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46230</v>
+        <v>45127</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45180</v>
+        <v>45415</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45357</v>
+        <v>45384</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45174</v>
+        <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46281</v>
+        <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45415</v>
+        <v>45104</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45195</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45491</v>
+        <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>46064</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45728</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45674</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45947</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45674</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45033</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45180</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45068</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45180</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45235</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46170</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>46183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>46184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45174</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45306</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45357</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45127</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45415</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45384</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45104</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45566</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>46064</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45300</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44911</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45728</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45674</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45947</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45674</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45033</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45180</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45068</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45180</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45235</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>46170</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>46183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>46184</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45174</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45306</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>46230</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45357</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45127</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45415</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45384</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45104</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44796</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45440</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45677</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45315</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44837</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45230</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45770</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46149</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE121"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44860</v>
+        <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,49 +1421,53 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>44860</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1497,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1526,49 +1530,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1586,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,17 +1602,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1622,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1638,42 +1642,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1691,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45798</v>
+        <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,10 +1707,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1743,46 +1747,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46064</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1852,42 +1852,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854</v>
+        <v>45056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2058,46 +2058,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45056</v>
+        <v>45222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2163,39 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45196</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45866</v>
+        <v>45551</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45117</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45126</v>
+        <v>45491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4068,13 +4068,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4117,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4131,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45566</v>
+        <v>45306</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4147,7 +4142,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4190,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4204,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46064</v>
+        <v>45233</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4220,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4263,7 +4258,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4277,10 +4272,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45300</v>
+        <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4288,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4336,7 +4331,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4350,10 +4345,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46071</v>
+        <v>45866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4361,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4409,7 +4404,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4423,10 +4418,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46071</v>
+        <v>45300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4434,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4482,7 +4477,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4496,10 +4491,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44911</v>
+        <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4511,13 +4506,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4560,7 +4550,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,10 +4564,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45833</v>
+        <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4590,7 +4580,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4633,7 +4623,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,10 +4637,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45110</v>
+        <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4663,7 +4653,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4696,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4710,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45728</v>
+        <v>45000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4769,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4783,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45299</v>
+        <v>45674</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4799,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4842,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4856,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45972</v>
+        <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4872,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4915,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45674</v>
+        <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4955,7 +4945,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +4988,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5002,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46136</v>
+        <v>45817</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5018,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>12.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5061,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45947</v>
+        <v>44824</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5091,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5134,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45674</v>
+        <v>45180</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5164,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5207,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5221,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45033</v>
+        <v>45972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5237,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5290,7 +5280,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5304,10 +5294,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45512</v>
+        <v>45993</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5319,8 +5309,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5363,7 +5358,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5377,10 +5372,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5392,13 +5387,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5441,7 +5431,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5458,7 +5448,7 @@
         <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5471,7 +5461,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5514,7 +5504,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5528,10 +5518,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45174</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5544,7 +5534,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5587,7 +5577,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5601,10 +5591,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45996</v>
+        <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5617,7 +5607,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5660,7 +5650,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5674,10 +5664,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45148</v>
+        <v>45126</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5689,8 +5679,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5733,7 +5728,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5747,10 +5742,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45217</v>
+        <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5763,7 +5758,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5806,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5820,10 +5815,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45110</v>
+        <v>46064</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5836,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5889,14 +5884,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45195</v>
+        <v>46071</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5909,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5952,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45243</v>
+        <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5982,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6025,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>45833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45180</v>
+        <v>45033</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6185,10 +6180,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45068</v>
+        <v>45104</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6254,14 +6249,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45551</v>
+        <v>45384</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45180</v>
+        <v>45622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45235</v>
+        <v>45300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45110</v>
+        <v>45512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44831</v>
+        <v>45947</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45889</v>
+        <v>46136</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6634,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45937</v>
+        <v>44911</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6711,8 +6706,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46170</v>
+        <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45148</v>
+        <v>44804</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46183</v>
+        <v>45937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>15.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45817</v>
+        <v>46170</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45629</v>
+        <v>45566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46184</v>
+        <v>45299</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44824</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46195</v>
+        <v>46183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45148</v>
+        <v>45243</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45233</v>
+        <v>44993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45174</v>
+        <v>45217</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45306</v>
+        <v>45196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44804</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46230</v>
+        <v>45566</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46230</v>
+        <v>45148</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46281</v>
+        <v>44494</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44993</v>
+        <v>45117</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45000</v>
+        <v>45127</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44494</v>
+        <v>45174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45357</v>
+        <v>45208</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45127</v>
+        <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45415</v>
+        <v>46230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45384</v>
+        <v>46230</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45208</v>
+        <v>45180</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45566</v>
+        <v>45357</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45104</v>
+        <v>45174</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45300</v>
+        <v>45415</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8736,14 +8736,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45622</v>
+        <v>45195</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45491</v>
+        <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8872,24 +8872,24 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S 177-2025</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45677</v>
+        <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 336-2024</t>
+          <t>S 177-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45328</v>
+        <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>25.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 181-2025</t>
+          <t>S 336-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45677</v>
+        <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>12.8</v>
+        <v>25.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9091,7 +9091,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 4689-2022</t>
+          <t>S 181-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44796</v>
+        <v>45677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>34</v>
+        <v>12.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 1864-2024</t>
+          <t>S 4689-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45440</v>
+        <v>44796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 180-2025</t>
+          <t>S 1864-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45677</v>
+        <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11.6</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 205-2024</t>
+          <t>S 180-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45315</v>
+        <v>45677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 2344-2023</t>
+          <t>S 205-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45106</v>
+        <v>45315</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>29.9</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 2345-2023</t>
+          <t>S 2344-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9473,7 +9473,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>31.6</v>
+        <v>29.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 5531-2022</t>
+          <t>S 2345-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9543,10 +9543,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44837</v>
+        <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>31.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9602,7 +9602,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 2350-2023</t>
+          <t>S 5531-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45106</v>
+        <v>44837</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>22.7</v>
+        <v>5.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 3886-2023</t>
+          <t>S 2350-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45230</v>
+        <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.9</v>
+        <v>22.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9748,7 +9748,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 1330-2025</t>
+          <t>S 3886-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45770</v>
+        <v>45230</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>12.7</v>
+        <v>4.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 1065-2026</t>
+          <t>S 1330-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46127</v>
+        <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9894,7 +9894,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 1381-2026</t>
+          <t>S 1065-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46147</v>
+        <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9967,7 +9967,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 1379-2026</t>
+          <t>S 1381-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9984,7 +9984,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10040,148 +10040,221 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
+          <t>S 1379-2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>S 1315-2026</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D120" s="1" t="n">
+      <c r="D121" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="E120" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
+      <c r="E121" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
         <v>2.6</v>
       </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>S 1377-2026</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D121" s="1" t="n">
+      <c r="D122" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="E121" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
+      <c r="E122" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
         <v>7</v>
       </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45798</v>
+        <v>44860</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>12.8</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,53 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1481,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44860</v>
+        <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1497,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1530,49 +1526,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1586,10 +1582,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46064</v>
+        <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1602,16 +1598,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1626,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1642,42 +1638,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46120</v>
+        <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1707,10 +1703,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1747,42 +1743,46 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1812,17 +1812,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1852,42 +1852,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45854</v>
+        <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45056</v>
+        <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2058,46 +2058,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45222</v>
+        <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,17 +2127,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2163,39 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44509</v>
+        <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44833</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>45196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45551</v>
+        <v>45866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>45300</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45491</v>
+        <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45306</v>
+        <v>45126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4141,8 +4141,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4190,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4204,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45233</v>
+        <v>45566</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4220,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4258,7 +4263,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4277,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44831</v>
+        <v>44911</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4287,8 +4292,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4331,7 +4341,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4345,10 +4355,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45866</v>
+        <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4361,7 +4371,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4404,7 +4414,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4418,10 +4428,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45300</v>
+        <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4434,7 +4444,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4477,7 +4487,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4491,10 +4501,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45148</v>
+        <v>45817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4507,7 +4517,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4550,7 +4560,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4564,10 +4574,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45110</v>
+        <v>45629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4580,7 +4590,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45235</v>
+        <v>45299</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,7 +4663,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4696,7 +4706,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4710,10 +4720,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45000</v>
+        <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4726,7 +4736,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4769,7 +4779,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4783,10 +4793,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45674</v>
+        <v>45972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4799,7 +4809,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4842,7 +4852,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4856,10 +4866,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45728</v>
+        <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4915,7 +4925,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45629</v>
+        <v>46071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4945,7 +4955,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4988,7 +4998,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45817</v>
+        <v>45674</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.7</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44824</v>
+        <v>45674</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,7 +5101,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5134,7 +5144,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45180</v>
+        <v>45033</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5164,7 +5174,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5207,7 +5217,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5221,10 +5231,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5236,8 +5246,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5280,7 +5295,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5294,10 +5309,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45993</v>
+        <v>45174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5309,13 +5324,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5358,7 +5368,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5372,10 +5382,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45996</v>
+        <v>45148</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5388,7 +5398,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5431,7 +5441,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5448,7 +5458,7 @@
         <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5471,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5504,7 +5514,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5518,10 +5528,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>45217</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5544,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5577,7 +5587,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5591,10 +5601,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5617,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5650,7 +5660,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5664,10 +5674,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45126</v>
+        <v>45833</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5679,13 +5689,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5733,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,10 +5747,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45148</v>
+        <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5758,7 +5763,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5806,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5811,14 +5816,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46064</v>
+        <v>45195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5836,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5879,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5893,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46071</v>
+        <v>45243</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5904,7 +5909,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5947,7 +5952,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5961,10 +5966,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46071</v>
+        <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +5982,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6025,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45833</v>
+        <v>45180</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6098,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45033</v>
+        <v>45068</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6171,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6176,14 +6181,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45104</v>
+        <v>45551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6201,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45384</v>
+        <v>45180</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,7 +6274,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6317,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45622</v>
+        <v>45235</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6347,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6390,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45300</v>
+        <v>45110</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6420,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6463,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45512</v>
+        <v>44831</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6493,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6536,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6550,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45947</v>
+        <v>46136</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6609,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46136</v>
+        <v>45947</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6634,7 +6639,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6677,7 +6682,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6691,10 +6696,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44911</v>
+        <v>45512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6706,13 +6711,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45889</v>
+        <v>45148</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44804</v>
+        <v>44824</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45937</v>
+        <v>45148</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46170</v>
+        <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45566</v>
+        <v>45233</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45299</v>
+        <v>45174</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>15.6</v>
+        <v>13.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45243</v>
+        <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44993</v>
+        <v>44804</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45217</v>
+        <v>46183</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>15.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45196</v>
+        <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45566</v>
+        <v>44993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45148</v>
+        <v>45000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7867,7 +7867,7 @@
         <v>44494</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45117</v>
+        <v>45357</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8013,7 +8013,7 @@
         <v>45127</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45174</v>
+        <v>45415</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45208</v>
+        <v>46230</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45110</v>
+        <v>46230</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46230</v>
+        <v>45384</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46230</v>
+        <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45180</v>
+        <v>46281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45357</v>
+        <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45174</v>
+        <v>45104</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45415</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8736,14 +8736,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45195</v>
+        <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46281</v>
+        <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8872,7 +8872,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8889,7 +8889,7 @@
         <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8945,24 +8945,24 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 177-2025</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45677</v>
+        <v>46290</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 336-2024</t>
+          <t>S 177-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45328</v>
+        <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>25.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9091,7 +9091,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 181-2025</t>
+          <t>S 336-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45677</v>
+        <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>12.8</v>
+        <v>25.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 4689-2022</t>
+          <t>S 181-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44796</v>
+        <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>34</v>
+        <v>12.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9237,7 +9237,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 1864-2024</t>
+          <t>S 4689-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45440</v>
+        <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 180-2025</t>
+          <t>S 1864-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45677</v>
+        <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.6</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 205-2024</t>
+          <t>S 180-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45315</v>
+        <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 2344-2023</t>
+          <t>S 205-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45106</v>
+        <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>29.9</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 2345-2023</t>
+          <t>S 2344-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9546,7 +9546,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>31.6</v>
+        <v>29.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9602,7 +9602,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 5531-2022</t>
+          <t>S 2345-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44837</v>
+        <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>31.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 2350-2023</t>
+          <t>S 5531-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45106</v>
+        <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>22.7</v>
+        <v>5.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9748,7 +9748,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 3886-2023</t>
+          <t>S 2350-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45230</v>
+        <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.9</v>
+        <v>22.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 1330-2025</t>
+          <t>S 3886-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45770</v>
+        <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>12.7</v>
+        <v>4.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9894,7 +9894,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 1065-2026</t>
+          <t>S 1330-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46127</v>
+        <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9967,7 +9967,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 1381-2026</t>
+          <t>S 1065-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46147</v>
+        <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10040,7 +10040,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 1379-2026</t>
+          <t>S 1381-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10057,7 +10057,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10113,148 +10113,221 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
+          <t>S 1379-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>S 1315-2026</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D121" s="1" t="n">
+      <c r="D122" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="E121" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
+      <c r="E122" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
         <v>2.6</v>
       </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>S 1377-2026</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D122" s="1" t="n">
+      <c r="D123" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="E122" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
+      <c r="E123" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
         <v>7</v>
       </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="2" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45677</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44860</v>
+        <v>45056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.8</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1421,49 +1421,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45414</v>
+        <v>44860</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1526,42 +1526,42 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
         <v>45222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46064</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1852,42 +1852,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46120</v>
+        <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1957,42 +1957,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854</v>
+        <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2062,42 +2062,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45056</v>
+        <v>45854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2163,39 +2163,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>45271</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>44796</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45770</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 64621-2021</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44511</v>
+        <v>44509</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3236,7 +3236,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 30978-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44509</v>
+        <v>44768</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30978-2022</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44768</v>
+        <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 64621-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44833</v>
+        <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45196</v>
+        <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45365</v>
+        <v>44824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45866</v>
+        <v>45180</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45300</v>
+        <v>45127</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44862</v>
+        <v>45174</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45126</v>
+        <v>45068</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4141,13 +4141,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4190,7 +4185,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4204,10 +4199,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45566</v>
+        <v>45208</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4220,7 +4215,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4280,7 +4275,7 @@
         <v>44911</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4341,7 +4336,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4358,7 +4353,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4371,7 +4366,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4414,7 +4409,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45728</v>
+        <v>44804</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4444,7 +4439,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4487,7 +4482,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,10 +4496,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45817</v>
+        <v>45365</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4517,7 +4512,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4560,7 +4555,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,10 +4569,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45629</v>
+        <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4590,7 +4585,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4633,7 +4628,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,10 +4642,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45299</v>
+        <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4662,8 +4657,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46064</v>
+        <v>45180</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4779,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45972</v>
+        <v>45148</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46071</v>
+        <v>45357</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46071</v>
+        <v>45551</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45674</v>
+        <v>45110</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45674</v>
+        <v>45110</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45033</v>
+        <v>45174</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45993</v>
+        <v>45566</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5246,13 +5246,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5295,7 +5290,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5309,10 +5304,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45174</v>
+        <v>45306</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5325,7 +5320,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5368,7 +5363,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5382,10 +5377,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45148</v>
+        <v>45033</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5398,7 +5393,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5441,7 +5436,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5455,10 +5450,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45996</v>
+        <v>45415</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5471,7 +5466,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5514,7 +5509,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5524,14 +5519,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45217</v>
+        <v>45195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5544,7 +5539,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5587,7 +5582,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5601,10 +5596,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>45299</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5617,7 +5612,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5660,7 +5655,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5674,10 +5669,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45833</v>
+        <v>45104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5690,7 +5685,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5733,7 +5728,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5747,10 +5742,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45996</v>
+        <v>45384</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5763,7 +5758,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5806,7 +5801,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5816,14 +5811,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45195</v>
+        <v>45243</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5836,7 +5831,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45243</v>
+        <v>45491</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5909,7 +5904,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5952,7 +5947,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45110</v>
+        <v>44993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5982,7 +5977,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6025,7 +6020,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45180</v>
+        <v>45622</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45068</v>
+        <v>45217</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6181,14 +6176,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45551</v>
+        <v>45233</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45180</v>
+        <v>44831</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45235</v>
+        <v>45196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6404,10 +6399,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45110</v>
+        <v>45300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44831</v>
+        <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46136</v>
+        <v>45566</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45947</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6639,7 +6634,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6696,10 +6691,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45512</v>
+        <v>45235</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6712,7 +6707,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6755,7 +6750,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45148</v>
+        <v>45300</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6785,7 +6780,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6828,7 +6823,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6842,10 +6837,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44824</v>
+        <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6858,7 +6853,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6901,7 +6896,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6915,10 +6910,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45148</v>
+        <v>45000</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6931,7 +6926,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6974,7 +6969,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6988,10 +6983,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45889</v>
+        <v>45674</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7004,7 +6999,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7047,7 +7042,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7061,10 +7056,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45233</v>
+        <v>44494</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7077,7 +7072,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7120,7 +7115,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7134,10 +7129,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45174</v>
+        <v>45629</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7150,7 +7145,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7193,7 +7188,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7207,10 +7202,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,7 +7218,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>12.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7266,7 +7261,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7280,10 +7275,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46170</v>
+        <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7296,7 +7291,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7339,7 +7334,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7353,10 +7348,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45306</v>
+        <v>45972</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7369,7 +7364,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7412,7 +7407,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7426,10 +7421,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44804</v>
+        <v>45993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7441,8 +7436,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46183</v>
+        <v>45996</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>15.6</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46184</v>
+        <v>45996</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>45866</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44993</v>
+        <v>46064</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45000</v>
+        <v>46071</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44494</v>
+        <v>46071</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45357</v>
+        <v>45833</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8010,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45127</v>
+        <v>45512</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45415</v>
+        <v>45947</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46230</v>
+        <v>46136</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46230</v>
+        <v>45889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45384</v>
+        <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45208</v>
+        <v>46170</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46281</v>
+        <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8521,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45566</v>
+        <v>46183</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>15.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45104</v>
+        <v>46195</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8653,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45300</v>
+        <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8726,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45622</v>
+        <v>46230</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45491</v>
+        <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>6.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8872,7 +8872,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8889,7 +8889,7 @@
         <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8962,7 +8962,7 @@
         <v>46290</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9035,7 +9035,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,24 +1138,24 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S 168-2025</t>
+          <t>A 38164-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45677</v>
+        <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>6.9</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -1208,255 +1208,260 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S 168-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>Mindre hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 168-2025 artfynd.xlsx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 168-2025 karta.png", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 168-2025 georefererad karta.tif", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 168-2025 FSC-klagomål.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 168-2025 FSC-klagomål mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 168-2025 tillsynsbegäran.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 168-2025 tillsynsbegäran mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 168-2025 prioriterade fågelarter.docx", "S 168-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>S 1328-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>27.2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Luddfingerört</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1328-2025 artfynd.xlsx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1328-2025 karta.png", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1328-2025 georefererad karta.tif", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1328-2025 FSC-klagomål.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1328-2025 FSC-klagomål mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1328-2025 tillsynsbegäran.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1328-2025 tillsynsbegäran mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1328-2025 prioriterade fågelarter.docx", "S 1328-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20426-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45056</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Hålnunneört</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1485,7 @@
         <v>44860</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1568,7 +1573,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1582,10 +1587,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45222</v>
+        <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1598,13 +1603,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1638,42 +1643,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1687,10 +1692,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45798</v>
+        <v>45222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1703,7 +1708,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1712,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1727,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1743,46 +1748,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45414</v>
+        <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1812,17 +1813,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1852,35 +1853,39 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1909,7 @@
         <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2014,7 @@
         <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2119,7 @@
         <v>45854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,24 +2207,24 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S 4458-2023</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45271</v>
+        <v>45056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2232,17 +2237,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>62.9</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2256,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2272,42 +2277,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S 172-2025</t>
+          <t>S 4458-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45677</v>
+        <v>45271</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2337,13 +2342,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>63.4</v>
+        <v>62.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2377,46 +2382,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lundbräsma</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 172-2025 artfynd.xlsx", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 172-2025 karta.png", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 172-2025 georefererad karta.tif", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 172-2025 FSC-klagomål.docx", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 172-2025 FSC-klagomål mail.docx", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 172-2025 tillsynsbegäran.docx", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 172-2025 tillsynsbegäran mail.docx", "S 172-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 172-2025 prioriterade fågelarter.docx", "S 172-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S 4679-2022</t>
+          <t>S 172-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2430,10 +2431,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44796</v>
+        <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2446,16 +2447,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>79.90000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2470,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2482,46 +2483,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Lamellsnäcka</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4679-2022 artfynd.xlsx", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 172-2025 artfynd.xlsx", "S 172-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4679-2022 karta.png", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 172-2025 karta.png", "S 172-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4679-2022 georefererad karta.tif", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 172-2025 georefererad karta.tif", "S 172-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4679-2022 FSC-klagomål.docx", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 172-2025 FSC-klagomål.docx", "S 172-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4679-2022 FSC-klagomål mail.docx", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 172-2025 FSC-klagomål mail.docx", "S 172-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4679-2022 tillsynsbegäran.docx", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 172-2025 tillsynsbegäran.docx", "S 172-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4679-2022 tillsynsbegäran mail.docx", "S 4679-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 172-2025 tillsynsbegäran mail.docx", "S 172-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 172-2025 prioriterade fågelarter.docx", "S 172-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S 3887-2023</t>
+          <t>S 4679-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45230</v>
+        <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2551,17 +2556,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.199999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2575,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2591,42 +2596,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Lamellsnäcka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 3887-2023 artfynd.xlsx", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4679-2022 artfynd.xlsx", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 3887-2023 karta.png", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4679-2022 karta.png", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 3887-2023 georefererad karta.tif", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4679-2022 georefererad karta.tif", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 3887-2023 FSC-klagomål.docx", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4679-2022 FSC-klagomål.docx", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 3887-2023 FSC-klagomål mail.docx", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4679-2022 FSC-klagomål mail.docx", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 3887-2023 tillsynsbegäran.docx", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4679-2022 tillsynsbegäran.docx", "S 4679-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 3887-2023 tillsynsbegäran mail.docx", "S 3887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4679-2022 tillsynsbegäran mail.docx", "S 4679-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S 2338-2023</t>
+          <t>S 3887-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2640,10 +2645,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45106</v>
+        <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,7 +2661,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>37.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2696,42 +2701,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 2338-2023 artfynd.xlsx", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 3887-2023 artfynd.xlsx", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 2338-2023 karta.png", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 3887-2023 karta.png", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 2338-2023 georefererad karta.tif", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 3887-2023 georefererad karta.tif", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 2338-2023 FSC-klagomål.docx", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 3887-2023 FSC-klagomål.docx", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 2338-2023 FSC-klagomål mail.docx", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 3887-2023 FSC-klagomål mail.docx", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 2338-2023 tillsynsbegäran.docx", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 3887-2023 tillsynsbegäran.docx", "S 3887-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 2338-2023 tillsynsbegäran mail.docx", "S 2338-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 3887-2023 tillsynsbegäran mail.docx", "S 3887-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S 1329-2025</t>
+          <t>S 2338-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2745,10 +2750,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45770</v>
+        <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,19 +2766,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>18.9</v>
+        <v>37.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2785,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2801,42 +2806,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1329-2025 artfynd.xlsx", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 2338-2023 artfynd.xlsx", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1329-2025 karta.png", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 2338-2023 karta.png", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1329-2025 georefererad karta.tif", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 2338-2023 georefererad karta.tif", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1329-2025 FSC-klagomål.docx", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 2338-2023 FSC-klagomål.docx", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1329-2025 FSC-klagomål mail.docx", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 2338-2023 FSC-klagomål mail.docx", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1329-2025 tillsynsbegäran.docx", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 2338-2023 tillsynsbegäran.docx", "S 2338-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1329-2025 tillsynsbegäran mail.docx", "S 1329-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 2338-2023 tillsynsbegäran mail.docx", "S 2338-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S 761-2025</t>
+          <t>S 1329-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,10 +2855,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45726</v>
+        <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2866,7 +2871,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14.5</v>
+        <v>18.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2875,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2893,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2906,46 +2911,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 761-2025 artfynd.xlsx", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1329-2025 artfynd.xlsx", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 761-2025 karta.png", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1329-2025 karta.png", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 761-2025 georefererad karta.tif", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1329-2025 georefererad karta.tif", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 761-2025 FSC-klagomål.docx", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1329-2025 FSC-klagomål.docx", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 761-2025 FSC-klagomål mail.docx", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1329-2025 FSC-klagomål mail.docx", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 761-2025 tillsynsbegäran.docx", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1329-2025 tillsynsbegäran.docx", "S 1329-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 761-2025 tillsynsbegäran mail.docx", "S 761-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 761-2025 prioriterade fågelarter.docx", "S 761-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1329-2025 tillsynsbegäran mail.docx", "S 1329-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S 836-2026</t>
+          <t>S 761-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2959,10 +2960,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46104</v>
+        <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2975,7 +2976,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>77.09999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -2984,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2999,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3015,46 +3016,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 836-2026 artfynd.xlsx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 761-2025 artfynd.xlsx", "S 761-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 836-2026 karta.png", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 761-2025 karta.png", "S 761-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 836-2026 georefererad karta.tif", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 761-2025 georefererad karta.tif", "S 761-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 836-2026 FSC-klagomål.docx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 761-2025 FSC-klagomål.docx", "S 761-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 836-2026 FSC-klagomål mail.docx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 761-2025 FSC-klagomål mail.docx", "S 761-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 836-2026 tillsynsbegäran.docx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 761-2025 tillsynsbegäran.docx", "S 761-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 836-2026 tillsynsbegäran mail.docx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 761-2025 tillsynsbegäran mail.docx", "S 761-2025")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 836-2026 prioriterade fågelarter.docx", "S 836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 761-2025 prioriterade fågelarter.docx", "S 761-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S 1376-2026</t>
+          <t>S 836-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3068,10 +3069,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46147</v>
+        <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3084,7 +3085,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>30.1</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3128,59 +3129,59 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1376-2026 artfynd.xlsx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 836-2026 artfynd.xlsx", "S 836-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1376-2026 karta.png", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 836-2026 karta.png", "S 836-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1376-2026 georefererad karta.tif", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 836-2026 georefererad karta.tif", "S 836-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1376-2026 FSC-klagomål.docx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 836-2026 FSC-klagomål.docx", "S 836-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1376-2026 FSC-klagomål mail.docx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 836-2026 FSC-klagomål mail.docx", "S 836-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1376-2026 tillsynsbegäran.docx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 836-2026 tillsynsbegäran.docx", "S 836-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1376-2026 tillsynsbegäran mail.docx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 836-2026 tillsynsbegäran mail.docx", "S 836-2026")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1376-2026 prioriterade fågelarter.docx", "S 1376-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 836-2026 prioriterade fågelarter.docx", "S 836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>S 1376-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44509</v>
+        <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,10 +3194,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>30.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3223,20 +3224,56 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1376-2026 artfynd.xlsx", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1376-2026 karta.png", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1376-2026 georefererad karta.tif", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1376-2026 FSC-klagomål.docx", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1376-2026 FSC-klagomål mail.docx", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1376-2026 tillsynsbegäran.docx", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1376-2026 tillsynsbegäran mail.docx", "S 1376-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1376-2026 prioriterade fågelarter.docx", "S 1376-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30978-2022</t>
+          <t>A 64621-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3250,10 +3287,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44768</v>
+        <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3303,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3309,7 +3346,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,10 +3360,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3376,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3382,7 +3419,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3396,10 +3433,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44833</v>
+        <v>44594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3449,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3455,7 +3492,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64621-2021</t>
+          <t>A 30978-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3469,10 +3506,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44511</v>
+        <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3522,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3528,7 +3565,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3542,10 +3579,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44596</v>
+        <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3595,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3601,7 +3638,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3618,7 +3655,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3668,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3674,7 +3711,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3688,10 +3725,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45674</v>
+        <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3784,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3761,10 +3798,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44824</v>
+        <v>45196</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3814,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3820,7 +3857,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3834,10 +3871,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45180</v>
+        <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3887,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3893,7 +3930,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3907,10 +3944,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45117</v>
+        <v>45866</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3960,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3966,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3980,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45127</v>
+        <v>45117</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4039,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4053,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45174</v>
+        <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4106,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4112,7 +4149,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4126,10 +4163,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45068</v>
+        <v>46064</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4179,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4185,7 +4222,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4199,10 +4236,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45208</v>
+        <v>45126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4212,6 +4249,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4258,7 +4300,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4272,10 +4314,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44911</v>
+        <v>45566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4287,13 +4329,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4336,7 +4373,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4350,10 +4387,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45110</v>
+        <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4403,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4409,7 +4446,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4423,10 +4460,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44804</v>
+        <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4476,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4482,7 +4519,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4496,10 +4533,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45365</v>
+        <v>45300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4512,7 +4549,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4555,7 +4592,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4569,10 +4606,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44862</v>
+        <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4585,7 +4622,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4628,7 +4665,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4642,10 +4679,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45126</v>
+        <v>44911</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4663,7 +4700,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4706,7 +4743,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,10 +4757,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45180</v>
+        <v>45728</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4736,7 +4773,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4779,7 +4816,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,10 +4830,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4809,7 +4846,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4852,7 +4889,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4866,10 +4903,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45357</v>
+        <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4882,7 +4919,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4925,7 +4962,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4935,14 +4972,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45551</v>
+        <v>45299</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4955,7 +4992,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4998,7 +5035,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,10 +5049,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45110</v>
+        <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5065,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5071,7 +5108,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,10 +5122,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45110</v>
+        <v>45947</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5138,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5144,7 +5181,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,10 +5195,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45174</v>
+        <v>45674</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5211,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5217,7 +5254,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,10 +5268,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45566</v>
+        <v>45512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5284,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5290,7 +5327,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5304,10 +5341,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45306</v>
+        <v>45993</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5319,8 +5356,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5363,7 +5405,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5377,10 +5419,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45033</v>
+        <v>45996</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5393,7 +5435,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5436,7 +5478,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5450,10 +5492,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45415</v>
+        <v>45674</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5466,7 +5508,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5509,7 +5551,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5519,14 +5561,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45195</v>
+        <v>45033</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5539,7 +5581,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5582,7 +5624,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5596,10 +5638,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45299</v>
+        <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5612,7 +5654,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5655,7 +5697,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5669,10 +5711,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45104</v>
+        <v>45174</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5685,7 +5727,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5728,7 +5770,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,10 +5784,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45384</v>
+        <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5758,7 +5800,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5801,7 +5843,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5815,10 +5857,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45243</v>
+        <v>45217</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5831,7 +5873,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5874,7 +5916,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5888,10 +5930,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45491</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5947,7 +5989,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5957,14 +5999,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44993</v>
+        <v>45195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5977,7 +6019,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6020,7 +6062,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6034,10 +6076,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45622</v>
+        <v>45243</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6050,7 +6092,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6093,7 +6135,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6107,10 +6149,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45217</v>
+        <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6123,7 +6165,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6166,7 +6208,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6180,10 +6222,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45233</v>
+        <v>45817</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6196,7 +6238,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6239,7 +6281,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6253,10 +6295,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44831</v>
+        <v>45629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6269,7 +6311,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6312,7 +6354,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6326,10 +6368,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45196</v>
+        <v>45180</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6342,7 +6384,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6385,7 +6427,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6399,10 +6441,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45300</v>
+        <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6415,7 +6457,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6458,7 +6500,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6468,14 +6510,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45148</v>
+        <v>45551</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6488,7 +6530,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6531,7 +6573,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6545,10 +6587,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45566</v>
+        <v>45180</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6561,7 +6603,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6604,7 +6646,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6618,10 +6660,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>45235</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6634,7 +6676,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6677,7 +6719,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6691,10 +6733,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45235</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6707,7 +6749,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6750,7 +6792,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6764,10 +6806,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45300</v>
+        <v>44831</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6780,7 +6822,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6823,7 +6865,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6837,10 +6879,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45148</v>
+        <v>45889</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6853,7 +6895,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6896,7 +6938,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6910,10 +6952,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45000</v>
+        <v>45148</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6926,7 +6968,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6969,7 +7011,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6983,10 +7025,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45674</v>
+        <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6999,7 +7041,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7042,7 +7084,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 24528-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7056,10 +7098,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44494</v>
+        <v>46170</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7072,7 +7114,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>13.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7115,7 +7157,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7129,10 +7171,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45629</v>
+        <v>44824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7145,7 +7187,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7188,7 +7230,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7202,10 +7244,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45817</v>
+        <v>46183</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7218,7 +7260,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7261,7 +7303,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7275,10 +7317,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45728</v>
+        <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7291,7 +7333,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7334,7 +7376,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7348,10 +7390,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45972</v>
+        <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7364,7 +7406,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7407,7 +7449,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7421,10 +7463,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45993</v>
+        <v>46195</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7436,13 +7478,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7485,7 +7522,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7499,10 +7536,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45996</v>
+        <v>45233</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7515,7 +7552,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7558,7 +7595,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7572,10 +7609,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45996</v>
+        <v>45174</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7631,7 +7668,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7645,10 +7682,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45866</v>
+        <v>45306</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7661,7 +7698,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7704,7 +7741,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7718,10 +7755,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46064</v>
+        <v>44804</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7734,7 +7771,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7777,7 +7814,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7791,10 +7828,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46071</v>
+        <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7807,7 +7844,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7850,7 +7887,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7864,10 +7901,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46071</v>
+        <v>46230</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7880,7 +7917,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7923,7 +7960,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7937,10 +7974,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45833</v>
+        <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7953,7 +7990,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7996,7 +8033,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8010,10 +8047,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45512</v>
+        <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8026,7 +8063,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8069,7 +8106,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8083,10 +8120,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45947</v>
+        <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8099,7 +8136,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8142,7 +8179,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8156,10 +8193,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46136</v>
+        <v>45357</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8172,7 +8209,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8215,7 +8252,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8229,10 +8266,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45889</v>
+        <v>45127</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8245,7 +8282,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8288,7 +8325,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8302,10 +8339,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45937</v>
+        <v>46290</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8318,7 +8355,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8361,7 +8398,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8375,10 +8412,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46170</v>
+        <v>45415</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8391,7 +8428,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>13.5</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8434,7 +8471,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8448,10 +8485,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46184</v>
+        <v>46290</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8501,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8507,7 +8544,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8521,10 +8558,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46183</v>
+        <v>45384</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8574,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>15.6</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8580,7 +8617,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8594,10 +8631,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46195</v>
+        <v>45208</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8647,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8653,7 +8690,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8667,10 +8704,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46230</v>
+        <v>45566</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8720,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8726,7 +8763,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8740,10 +8777,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46230</v>
+        <v>45104</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8793,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8799,7 +8836,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8813,10 +8850,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46281</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8866,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8872,7 +8909,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8886,10 +8923,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46290</v>
+        <v>45622</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8902,7 +8939,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8945,7 +8982,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8959,10 +8996,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46290</v>
+        <v>45491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8975,7 +9012,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9035,7 +9072,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9145,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9181,7 +9218,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9254,7 +9291,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9327,7 +9364,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9400,7 +9437,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9473,7 +9510,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9546,7 +9583,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9619,7 +9656,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9692,7 +9729,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9765,7 +9802,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9838,7 +9875,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9911,7 +9948,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9984,7 +10021,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10057,7 +10094,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10130,7 +10167,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10203,7 +10240,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10276,7 +10313,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE123"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45677</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45770</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44860</v>
+        <v>45798</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1531,49 +1531,53 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1603,17 +1607,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1627,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1643,42 +1647,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1692,10 +1696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1711,14 +1715,14 @@
         <v>6.4</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1732,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1748,42 +1752,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1797,10 +1801,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45798</v>
+        <v>44860</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1813,16 +1817,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>12.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1837,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1846,53 +1850,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1962,42 +1962,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46120</v>
+        <v>45414</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2027,16 +2027,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2067,42 +2067,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45854</v>
+        <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2132,17 +2132,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2168,46 +2168,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45056</v>
+        <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2273,39 +2273,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
         <v>45271</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44509</v>
+        <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45196</v>
+        <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3940,14 +3940,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45866</v>
+        <v>45551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4003,7 +4003,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45117</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46064</v>
+        <v>45491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4222,7 +4222,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45126</v>
+        <v>45306</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4251,13 +4251,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4300,7 +4295,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45566</v>
+        <v>45233</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4330,7 +4325,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46071</v>
+        <v>45866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46071</v>
+        <v>44831</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4476,7 +4471,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4519,7 +4514,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4533,10 +4528,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45300</v>
+        <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4549,7 +4544,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4592,7 +4587,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45833</v>
+        <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4622,7 +4617,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4665,7 +4660,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44911</v>
+        <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4694,13 +4689,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4743,7 +4733,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4757,10 +4747,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45728</v>
+        <v>45000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4773,7 +4763,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4816,7 +4806,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4830,10 +4820,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45110</v>
+        <v>45300</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4846,7 +4836,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4889,7 +4879,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4903,10 +4893,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45972</v>
+        <v>45674</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4919,7 +4909,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4962,7 +4952,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4976,10 +4966,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45299</v>
+        <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4992,7 +4982,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5035,7 +5025,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5049,10 +5039,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46136</v>
+        <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5065,7 +5055,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5108,7 +5098,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5122,10 +5112,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45947</v>
+        <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5138,7 +5128,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5181,7 +5171,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5195,10 +5185,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45674</v>
+        <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5211,7 +5201,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5254,7 +5244,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,10 +5258,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45512</v>
+        <v>45833</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5284,7 +5274,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5327,7 +5317,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5341,10 +5331,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45993</v>
+        <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5354,11 +5344,6 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5405,7 +5390,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5419,10 +5404,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45996</v>
+        <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5435,7 +5420,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5478,7 +5463,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5492,10 +5477,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45674</v>
+        <v>45972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5508,7 +5493,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5551,7 +5536,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5565,10 +5550,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45033</v>
+        <v>45993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5578,6 +5563,11 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5624,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5638,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45996</v>
+        <v>45365</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5654,7 +5644,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5697,7 +5687,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5711,10 +5701,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45174</v>
+        <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5727,7 +5717,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5770,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5784,10 +5774,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45148</v>
+        <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5800,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5843,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45217</v>
+        <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5873,7 +5863,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5916,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5930,10 +5920,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45126</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5945,8 +5935,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5989,7 +5984,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5999,14 +5994,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45195</v>
+        <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6019,7 +6014,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6062,7 +6057,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6076,10 +6071,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45243</v>
+        <v>45512</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6092,7 +6087,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6135,7 +6130,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45110</v>
+        <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6165,7 +6160,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45817</v>
+        <v>45033</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>12.7</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45629</v>
+        <v>45104</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6311,7 +6306,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6354,7 +6349,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6368,10 +6363,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45180</v>
+        <v>45384</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6384,7 +6379,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6427,7 +6422,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45068</v>
+        <v>45622</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6457,7 +6452,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6500,7 +6495,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6510,14 +6505,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45551</v>
+        <v>46136</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6530,7 +6525,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6573,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6587,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45180</v>
+        <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6603,7 +6598,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6646,7 +6641,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6660,10 +6655,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45235</v>
+        <v>45817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6676,7 +6671,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>12.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6719,7 +6714,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6733,10 +6728,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45110</v>
+        <v>45300</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6749,7 +6744,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6792,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6806,10 +6801,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44831</v>
+        <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6822,7 +6817,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6865,7 +6860,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6879,10 +6874,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45889</v>
+        <v>45937</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6890,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6938,7 +6933,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6952,10 +6947,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45148</v>
+        <v>46184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6963,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7011,7 +7006,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7025,10 +7020,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45937</v>
+        <v>46183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7036,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>15.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7084,7 +7079,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24528-2026</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7098,10 +7093,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46170</v>
+        <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7109,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7157,7 +7152,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7171,10 +7166,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44824</v>
+        <v>44911</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7186,8 +7181,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46183</v>
+        <v>44804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>15.6</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45148</v>
+        <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46184</v>
+        <v>45299</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45233</v>
+        <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45174</v>
+        <v>45243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45306</v>
+        <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44804</v>
+        <v>45217</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7814,7 +7814,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46230</v>
+        <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46230</v>
+        <v>45566</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7960,7 +7960,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44993</v>
+        <v>45148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8033,7 +8033,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45000</v>
+        <v>46290</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44494</v>
+        <v>46290</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8179,7 +8179,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45357</v>
+        <v>44494</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45127</v>
+        <v>45117</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8325,7 +8325,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46290</v>
+        <v>45127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8398,7 +8398,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8412,10 +8412,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45415</v>
+        <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46290</v>
+        <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45384</v>
+        <v>45110</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45208</v>
+        <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45566</v>
+        <v>45357</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45104</v>
+        <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8836,7 +8836,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8919,14 +8919,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45622</v>
+        <v>45195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8982,24 +8982,24 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>S 177-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45491</v>
+        <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 177-2025</t>
+          <t>S 336-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9069,10 +9069,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45677</v>
+        <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.800000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9128,7 +9128,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 336-2024</t>
+          <t>S 181-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45328</v>
+        <v>45677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>25.6</v>
+        <v>12.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9201,7 +9201,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 181-2025</t>
+          <t>S 4689-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45677</v>
+        <v>44796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>12.8</v>
+        <v>34</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9274,7 +9274,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 4689-2022</t>
+          <t>S 1864-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9288,10 +9288,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44796</v>
+        <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9347,7 +9347,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 1864-2024</t>
+          <t>S 180-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9361,10 +9361,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45440</v>
+        <v>45677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>11.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9420,7 +9420,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 180-2025</t>
+          <t>S 205-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45677</v>
+        <v>45315</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 205-2024</t>
+          <t>S 2344-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45315</v>
+        <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>29.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 2344-2023</t>
+          <t>S 2345-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9583,7 +9583,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>29.9</v>
+        <v>31.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9639,7 +9639,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 2345-2023</t>
+          <t>S 5531-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45106</v>
+        <v>44837</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>31.6</v>
+        <v>5.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9712,7 +9712,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 5531-2022</t>
+          <t>S 2350-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44837</v>
+        <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.3</v>
+        <v>22.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9785,7 +9785,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 2350-2023</t>
+          <t>S 3886-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45106</v>
+        <v>45230</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>22.7</v>
+        <v>4.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 3886-2023</t>
+          <t>S 1330-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45230</v>
+        <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.9</v>
+        <v>12.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9931,7 +9931,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 1330-2025</t>
+          <t>S 1065-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45770</v>
+        <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>12.7</v>
+        <v>4.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10004,7 +10004,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 1065-2026</t>
+          <t>S 1381-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46127</v>
+        <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10077,7 +10077,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 1381-2026</t>
+          <t>S 1379-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10094,7 +10094,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10150,7 +10150,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 1379-2026</t>
+          <t>S 1315-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10164,83 +10164,83 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S 1377-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="E121" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>S 1315-2026</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>46149</v>
-      </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10292,79 +10292,6 @@
         <v>0</v>
       </c>
       <c r="V122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>S 1377-2026</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>46147</v>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45677</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45770</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45798</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44860</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45414</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>45271</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>45491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>45306</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45233</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44831</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45300</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>45674</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45833</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>45993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>45365</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45126</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45512</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45033</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45104</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45384</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45622</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>46136</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45300</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>45937</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>46183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44911</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45299</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>46230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45217</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45566</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>46290</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>46290</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44494</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45117</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45110</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45357</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45315</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44837</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45230</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46149</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45677</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45770</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45798</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>46120</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44860</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45854</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45414</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45056</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>45271</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>45491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>45306</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45233</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44831</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45300</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>45674</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46064</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>45728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45833</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>45993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>45365</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45126</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>45512</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>45033</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45104</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45384</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45622</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>46136</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45300</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>45937</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>46183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>44911</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45299</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>46230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>46230</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45243</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>45217</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45566</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45148</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>46290</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>46290</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44494</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45117</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45110</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45357</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45315</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44837</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45230</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46149</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S 168-2025</t>
+          <t>S 4458-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45677</v>
+        <v>45271</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>62.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1318,266 +1318,263 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Lundbräsma
+Lömsk flugsvamp</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S 168-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Mindre hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 168-2025 artfynd.xlsx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 168-2025 karta.png", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 168-2025 georefererad karta.tif", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 168-2025 FSC-klagomål.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 168-2025 FSC-klagomål mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 168-2025 tillsynsbegäran.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 168-2025 tillsynsbegäran mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 168-2025 prioriterade fågelarter.docx", "S 168-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>S 1328-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>27.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Luddfingerört</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1328-2025 artfynd.xlsx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1328-2025 karta.png", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1328-2025 georefererad karta.tif", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1328-2025 FSC-klagomål.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1328-2025 FSC-klagomål mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1328-2025 tillsynsbegäran.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1328-2025 tillsynsbegäran mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1328-2025 prioriterade fågelarter.docx", "S 1328-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24688-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45798</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1591,10 +1588,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46064</v>
+        <v>44860</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1607,16 +1604,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>12.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1631,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1640,49 +1637,49 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,10 +1693,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46120</v>
+        <v>45414</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,16 +1709,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1736,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1752,42 +1749,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1801,10 +1798,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44860</v>
+        <v>45222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,13 +1814,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1850,49 +1847,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1906,10 +1903,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45854</v>
+        <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1922,17 +1919,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1946,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1962,42 +1959,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2011,10 +2008,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45414</v>
+        <v>46120</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2027,17 +2024,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2051,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2067,42 +2064,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2116,10 +2113,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45056</v>
+        <v>45854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2132,16 +2129,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2156,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2168,46 +2165,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2221,10 +2218,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45222</v>
+        <v>45056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2237,17 +2234,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2273,63 +2270,63 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S 4458-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45271</v>
+        <v>45798</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2342,17 +2339,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>62.9</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2366,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2378,39 +2375,43 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -2434,7 +2435,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2543,7 +2544,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2648,7 +2649,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2753,7 +2754,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2858,7 +2859,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2963,7 +2964,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3073,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3181,7 +3182,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3290,7 +3291,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3363,7 +3364,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3436,7 +3437,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3509,7 +3510,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3582,7 +3583,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3655,7 +3656,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3728,7 +3729,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3784,7 +3785,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3798,10 +3799,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45674</v>
+        <v>45196</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3814,7 +3815,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3857,7 +3858,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3871,10 +3872,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3887,7 +3888,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3930,7 +3931,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3940,14 +3941,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45551</v>
+        <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3960,7 +3961,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4003,7 +4004,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4017,10 +4018,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4033,7 +4034,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4076,7 +4077,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,10 +4091,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45110</v>
+        <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4106,7 +4107,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4149,7 +4150,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4163,10 +4164,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45491</v>
+        <v>45126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4178,8 +4179,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4222,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4236,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45306</v>
+        <v>45566</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4252,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4295,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4309,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45233</v>
+        <v>44911</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4324,8 +4330,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4368,7 +4379,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4382,10 +4393,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45866</v>
+        <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4398,7 +4409,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4441,7 +4452,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4455,10 +4466,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44831</v>
+        <v>45817</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4471,7 +4482,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4514,7 +4525,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4528,10 +4539,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45148</v>
+        <v>45629</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4544,7 +4555,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4587,7 +4598,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4601,10 +4612,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45110</v>
+        <v>45299</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4617,7 +4628,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4660,7 +4671,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4674,10 +4685,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45235</v>
+        <v>46064</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4690,7 +4701,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4733,7 +4744,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4747,10 +4758,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45000</v>
+        <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4763,7 +4774,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4806,7 +4817,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4820,10 +4831,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45300</v>
+        <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4836,7 +4847,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4879,7 +4890,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4893,10 +4904,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45674</v>
+        <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4909,7 +4920,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4952,7 +4963,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4966,10 +4977,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46064</v>
+        <v>45674</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4982,7 +4993,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5025,7 +5036,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5039,10 +5050,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46071</v>
+        <v>45674</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5055,7 +5066,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5098,7 +5109,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5112,10 +5123,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46071</v>
+        <v>45033</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5128,7 +5139,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5171,7 +5182,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5185,10 +5196,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45728</v>
+        <v>45833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5201,7 +5212,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5244,7 +5255,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5258,10 +5269,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45833</v>
+        <v>45174</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5274,7 +5285,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5317,7 +5328,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5331,10 +5342,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44824</v>
+        <v>45148</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5347,7 +5358,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5390,7 +5401,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5404,10 +5415,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45180</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5420,7 +5431,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5463,7 +5474,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5477,10 +5488,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45972</v>
+        <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5493,7 +5504,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5536,7 +5547,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5546,14 +5557,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45993</v>
+        <v>45195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5565,13 +5576,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5614,7 +5620,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5628,10 +5634,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45365</v>
+        <v>45243</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5644,7 +5650,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5687,7 +5693,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5701,10 +5707,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44862</v>
+        <v>45972</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5717,7 +5723,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5760,7 +5766,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5774,10 +5780,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45996</v>
+        <v>45110</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5790,7 +5796,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5833,7 +5839,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5847,10 +5853,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45996</v>
+        <v>45180</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5863,7 +5869,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5906,7 +5912,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5920,10 +5926,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45126</v>
+        <v>45068</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5935,13 +5941,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5984,7 +5985,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5998,10 +5999,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45148</v>
+        <v>45993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6013,8 +6014,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6057,7 +6063,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6071,10 +6077,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45512</v>
+        <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6087,7 +6093,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6130,7 +6136,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6144,10 +6150,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45947</v>
+        <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6160,7 +6166,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6203,7 +6209,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,14 +6219,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45033</v>
+        <v>45551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6233,7 +6239,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6276,7 +6282,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6290,10 +6296,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45104</v>
+        <v>46136</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6306,7 +6312,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6349,7 +6355,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6363,10 +6369,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45384</v>
+        <v>45947</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6379,7 +6385,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6422,7 +6428,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6436,10 +6442,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45622</v>
+        <v>45180</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6458,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6495,7 +6501,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6509,10 +6515,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46136</v>
+        <v>45235</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6525,7 +6531,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6568,7 +6574,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6582,10 +6588,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45629</v>
+        <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6598,7 +6604,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6641,7 +6647,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6655,10 +6661,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45817</v>
+        <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6671,7 +6677,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6714,7 +6720,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6728,10 +6734,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45300</v>
+        <v>45866</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6744,7 +6750,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6787,7 +6793,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6801,10 +6807,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45889</v>
+        <v>45512</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6823,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6860,7 +6866,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6874,10 +6880,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45937</v>
+        <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6890,7 +6896,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6933,7 +6939,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6947,10 +6953,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46184</v>
+        <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6963,7 +6969,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7006,7 +7012,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7020,10 +7026,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46183</v>
+        <v>45889</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7036,7 +7042,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>15.6</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7079,7 +7085,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7093,10 +7099,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46195</v>
+        <v>45148</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7109,7 +7115,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7152,7 +7158,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7166,10 +7172,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44911</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7181,13 +7187,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7230,7 +7231,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7244,10 +7245,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44804</v>
+        <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7261,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7303,7 +7304,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7317,10 +7318,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45566</v>
+        <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7333,7 +7334,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7376,7 +7377,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7390,10 +7391,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45299</v>
+        <v>46183</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7406,7 +7407,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>15.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7449,7 +7450,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7463,10 +7464,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46230</v>
+        <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7479,7 +7480,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7522,7 +7523,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7536,10 +7537,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46230</v>
+        <v>45306</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7552,7 +7553,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7595,7 +7596,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7609,10 +7610,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45243</v>
+        <v>44804</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7625,7 +7626,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7668,7 +7669,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7682,10 +7683,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44993</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7698,7 +7699,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7741,7 +7742,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7755,10 +7756,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45217</v>
+        <v>44993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7771,7 +7772,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7814,7 +7815,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7828,10 +7829,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45196</v>
+        <v>45000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7844,7 +7845,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7887,7 +7888,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7901,10 +7902,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45566</v>
+        <v>46230</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7917,7 +7918,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7960,7 +7961,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7974,10 +7975,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45148</v>
+        <v>46230</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7990,7 +7991,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8033,7 +8034,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8047,10 +8048,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46290</v>
+        <v>44494</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8063,7 +8064,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8106,7 +8107,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8120,10 +8121,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46290</v>
+        <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8136,7 +8137,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8179,7 +8180,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8193,10 +8194,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44494</v>
+        <v>45127</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8209,7 +8210,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8252,7 +8253,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8266,10 +8267,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45117</v>
+        <v>45415</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8282,7 +8283,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8325,7 +8326,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8339,10 +8340,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45127</v>
+        <v>45384</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8355,7 +8356,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8398,7 +8399,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8412,10 +8413,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45174</v>
+        <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8428,7 +8429,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8471,7 +8472,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8485,10 +8486,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45208</v>
+        <v>45566</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8544,7 +8545,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8558,10 +8559,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45110</v>
+        <v>45104</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8574,7 +8575,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8617,7 +8618,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8631,10 +8632,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45180</v>
+        <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8647,7 +8648,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8690,7 +8691,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8704,10 +8705,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45357</v>
+        <v>46290</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8720,7 +8721,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8763,7 +8764,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8777,10 +8778,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45174</v>
+        <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8793,7 +8794,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8836,7 +8837,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8850,10 +8851,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45415</v>
+        <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8866,7 +8867,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8909,7 +8910,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8919,14 +8920,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45195</v>
+        <v>45491</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8939,7 +8940,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8999,7 +9000,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9072,7 +9073,7 @@
         <v>45328</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9145,7 +9146,7 @@
         <v>45677</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,7 +9219,7 @@
         <v>44796</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9291,7 +9292,7 @@
         <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,7 +9365,7 @@
         <v>45677</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9437,7 +9438,7 @@
         <v>45315</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9510,7 +9511,7 @@
         <v>45106</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9583,7 +9584,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,7 +9657,7 @@
         <v>44837</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9729,7 +9730,7 @@
         <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,7 +9803,7 @@
         <v>45230</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9875,7 +9876,7 @@
         <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9948,7 +9949,7 @@
         <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10021,7 +10022,7 @@
         <v>46147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10094,7 +10095,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10167,7 +10168,7 @@
         <v>46149</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10240,7 +10241,7 @@
         <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46281</v>
+        <v>45798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -1204,482 +1204,487 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 38164-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>S 4458-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45271</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>62.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Lundbräsma
 Lömsk flugsvamp</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>S 168-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45677</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 168-2025 artfynd.xlsx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 168-2025 karta.png", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 168-2025 georefererad karta.tif", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 168-2025 FSC-klagomål.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 168-2025 FSC-klagomål mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 168-2025 tillsynsbegäran.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 168-2025 tillsynsbegäran mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 168-2025 prioriterade fågelarter.docx", "S 168-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>S 1328-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>27.2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Luddfingerört</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1328-2025 artfynd.xlsx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1328-2025 karta.png", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1328-2025 georefererad karta.tif", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1328-2025 FSC-klagomål.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1328-2025 FSC-klagomål mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1328-2025 tillsynsbegäran.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1328-2025 tillsynsbegäran mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1328-2025 prioriterade fågelarter.docx", "S 1328-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 50118-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44860</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1709,17 +1714,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1733,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1749,42 +1754,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,14 +1822,14 @@
         <v>6.4</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1838,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1854,42 +1859,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1903,10 +1908,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46064</v>
+        <v>44860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1919,16 +1924,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>12.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1943,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1952,49 +1957,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,10 +2013,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2024,16 +2029,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2048,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2064,42 +2069,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2113,10 +2118,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2129,7 +2134,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2169,35 +2174,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
@@ -2221,7 +2226,7 @@
         <v>45056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2309,7 +2314,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2323,10 +2328,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45798</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2339,7 +2344,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2348,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2363,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2379,39 +2384,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2435,7 +2436,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2544,7 +2545,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2649,7 +2650,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2754,7 +2755,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2859,7 +2860,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,7 +2965,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3073,7 +3074,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3182,7 +3183,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3291,7 +3292,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3364,7 +3365,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3437,7 +3438,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3510,7 +3511,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3583,7 +3584,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3657,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3729,7 +3730,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3785,7 +3786,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3799,10 +3800,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45196</v>
+        <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3815,7 +3816,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3858,7 +3859,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3872,10 +3873,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3888,7 +3889,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3931,7 +3932,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3941,14 +3942,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45117</v>
+        <v>45551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3961,7 +3962,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4004,7 +4005,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4018,10 +4019,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44862</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4034,7 +4035,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4077,7 +4078,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4091,10 +4092,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45300</v>
+        <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4107,7 +4108,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4150,7 +4151,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4164,10 +4165,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45126</v>
+        <v>45306</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4179,13 +4180,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4224,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4238,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45566</v>
+        <v>45233</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4254,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4297,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4311,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44911</v>
+        <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4330,13 +4326,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4379,7 +4370,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4393,10 +4384,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45110</v>
+        <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4409,7 +4400,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4452,7 +4443,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4466,10 +4457,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45817</v>
+        <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4482,7 +4473,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>12.7</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4525,7 +4516,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4539,10 +4530,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45629</v>
+        <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4555,7 +4546,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4598,7 +4589,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4612,10 +4603,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45299</v>
+        <v>45000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4628,7 +4619,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4671,7 +4662,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4685,10 +4676,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46064</v>
+        <v>45300</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4701,7 +4692,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4744,7 +4735,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4758,10 +4749,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46071</v>
+        <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4774,7 +4765,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4817,7 +4808,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4831,10 +4822,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4847,7 +4838,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4890,7 +4881,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4904,10 +4895,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45728</v>
+        <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4920,7 +4911,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4963,7 +4954,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4977,10 +4968,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45674</v>
+        <v>46071</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4993,7 +4984,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5036,7 +5027,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5050,10 +5041,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45674</v>
+        <v>44824</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5066,7 +5057,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5109,7 +5100,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5123,10 +5114,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45033</v>
+        <v>45180</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5139,7 +5130,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5199,7 +5190,7 @@
         <v>45833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5255,7 +5246,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5269,10 +5260,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45174</v>
+        <v>45728</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5285,7 +5276,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5328,7 +5319,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5342,10 +5333,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45148</v>
+        <v>45365</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5401,7 +5392,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5415,10 +5406,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45217</v>
+        <v>45629</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5431,7 +5422,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5474,7 +5465,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5488,10 +5479,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45110</v>
+        <v>45817</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5504,7 +5495,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>12.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5547,7 +5538,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5557,14 +5548,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45195</v>
+        <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5577,7 +5568,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5620,7 +5611,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5634,10 +5625,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45243</v>
+        <v>45512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5650,7 +5641,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5693,7 +5684,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5707,10 +5698,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45972</v>
+        <v>45126</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5722,8 +5713,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5766,7 +5762,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45110</v>
+        <v>45148</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5796,7 +5792,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5839,7 +5835,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5853,10 +5849,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45180</v>
+        <v>45972</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5869,7 +5865,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5912,7 +5908,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5926,10 +5922,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45068</v>
+        <v>45947</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5942,7 +5938,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6002,7 +5998,7 @@
         <v>45993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6080,7 +6076,7 @@
         <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6153,7 +6149,7 @@
         <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6209,7 +6205,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6219,14 +6215,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45551</v>
+        <v>46136</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6239,7 +6235,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6282,7 +6278,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6296,10 +6292,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46136</v>
+        <v>45866</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6312,7 +6308,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6355,7 +6351,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6369,10 +6365,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45947</v>
+        <v>45033</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6385,7 +6381,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6428,7 +6424,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6442,10 +6438,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45180</v>
+        <v>45889</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6458,7 +6454,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6501,7 +6497,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6515,10 +6511,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45235</v>
+        <v>45937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6531,7 +6527,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6574,7 +6570,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6588,10 +6584,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45110</v>
+        <v>46184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6604,7 +6600,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6647,7 +6643,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6661,10 +6657,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44831</v>
+        <v>46183</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6677,7 +6673,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>15.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6720,7 +6716,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6734,10 +6730,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45866</v>
+        <v>45104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6750,7 +6746,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6793,7 +6789,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6807,10 +6803,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45512</v>
+        <v>45384</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6823,7 +6819,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6866,7 +6862,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6880,10 +6876,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45148</v>
+        <v>45622</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6896,7 +6892,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6939,7 +6935,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6953,10 +6949,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44824</v>
+        <v>46195</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6969,7 +6965,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7012,7 +7008,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7026,10 +7022,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45889</v>
+        <v>45300</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7042,7 +7038,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7085,7 +7081,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7099,10 +7095,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45148</v>
+        <v>44911</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,8 +7110,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7158,7 +7159,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7172,10 +7173,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>46230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7188,7 +7189,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7231,7 +7232,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7245,10 +7246,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45233</v>
+        <v>44804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7261,7 +7262,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7304,7 +7305,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7318,10 +7319,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45174</v>
+        <v>46230</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7334,7 +7335,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7377,7 +7378,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7391,10 +7392,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46183</v>
+        <v>45566</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7407,7 +7408,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>15.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7450,7 +7451,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7464,10 +7465,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46184</v>
+        <v>45299</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7480,7 +7481,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7523,7 +7524,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7537,10 +7538,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45306</v>
+        <v>45243</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7553,7 +7554,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7596,7 +7597,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7610,10 +7611,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44804</v>
+        <v>44993</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7626,7 +7627,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7669,7 +7670,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7683,10 +7684,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>45217</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7699,7 +7700,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7742,7 +7743,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7756,10 +7757,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44993</v>
+        <v>46290</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7772,7 +7773,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7815,7 +7816,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7829,10 +7830,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45000</v>
+        <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7845,7 +7846,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7888,7 +7889,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7902,10 +7903,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46230</v>
+        <v>46290</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7918,7 +7919,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7961,7 +7962,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7975,10 +7976,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46230</v>
+        <v>45566</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7991,7 +7992,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8034,7 +8035,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8048,10 +8049,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44494</v>
+        <v>45148</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8064,7 +8065,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8107,7 +8108,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 41398-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8121,10 +8122,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45357</v>
+        <v>46300</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8137,7 +8138,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8180,7 +8181,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8194,10 +8195,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45127</v>
+        <v>44494</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8210,7 +8211,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8253,7 +8254,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8267,10 +8268,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45415</v>
+        <v>45117</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8283,7 +8284,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8326,7 +8327,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8340,10 +8341,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45384</v>
+        <v>45127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8356,7 +8357,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8399,7 +8400,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8413,10 +8414,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45208</v>
+        <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8429,7 +8430,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8472,7 +8473,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8486,10 +8487,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45566</v>
+        <v>45208</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8545,7 +8546,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8559,10 +8560,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45104</v>
+        <v>45110</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8575,7 +8576,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8618,7 +8619,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8632,10 +8633,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8648,7 +8649,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8691,7 +8692,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8705,10 +8706,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46290</v>
+        <v>45357</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8721,7 +8722,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8764,7 +8765,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8778,10 +8779,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45622</v>
+        <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8794,7 +8795,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8837,7 +8838,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8851,10 +8852,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46290</v>
+        <v>45415</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8867,7 +8868,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8910,7 +8911,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8920,14 +8921,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45491</v>
+        <v>45195</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8940,7 +8941,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8983,24 +8984,24 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S 177-2025</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45677</v>
+        <v>45491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9013,7 +9014,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9056,7 +9057,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S 336-2024</t>
+          <t>S 177-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9070,10 +9071,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45328</v>
+        <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9086,7 +9087,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>25.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9129,7 +9130,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S 181-2025</t>
+          <t>S 336-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9143,10 +9144,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45677</v>
+        <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9159,7 +9160,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>12.8</v>
+        <v>25.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9202,7 +9203,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S 4689-2022</t>
+          <t>S 181-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9216,10 +9217,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44796</v>
+        <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9232,7 +9233,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>34</v>
+        <v>12.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9275,7 +9276,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S 1864-2024</t>
+          <t>S 4689-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9289,10 +9290,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45440</v>
+        <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9305,7 +9306,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9348,7 +9349,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S 180-2025</t>
+          <t>S 1864-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9362,10 +9363,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45677</v>
+        <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9378,7 +9379,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11.6</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9421,7 +9422,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S 205-2024</t>
+          <t>S 180-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9435,10 +9436,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45315</v>
+        <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9451,7 +9452,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9494,7 +9495,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S 2344-2023</t>
+          <t>S 205-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9508,10 +9509,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45106</v>
+        <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9524,7 +9525,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>29.9</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9567,7 +9568,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S 2345-2023</t>
+          <t>S 2344-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9584,7 +9585,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9597,7 +9598,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>31.6</v>
+        <v>29.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9640,7 +9641,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S 5531-2022</t>
+          <t>S 2345-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9654,10 +9655,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44837</v>
+        <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9670,7 +9671,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>31.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9713,7 +9714,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S 2350-2023</t>
+          <t>S 5531-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9727,10 +9728,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45106</v>
+        <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9743,7 +9744,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>22.7</v>
+        <v>5.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9786,7 +9787,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S 3886-2023</t>
+          <t>S 2350-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9800,10 +9801,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45230</v>
+        <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9816,7 +9817,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.9</v>
+        <v>22.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9859,7 +9860,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S 1330-2025</t>
+          <t>S 3886-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9873,10 +9874,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45770</v>
+        <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9889,7 +9890,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>12.7</v>
+        <v>4.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9932,7 +9933,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S 1065-2026</t>
+          <t>S 1330-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9946,10 +9947,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46127</v>
+        <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9962,7 +9963,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10005,7 +10006,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S 1381-2026</t>
+          <t>S 1065-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10019,10 +10020,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46147</v>
+        <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10035,7 +10036,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10078,7 +10079,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 1379-2026</t>
+          <t>S 1381-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10095,7 +10096,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10108,7 +10109,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10151,148 +10152,221 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
+          <t>S 1379-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>S 1315-2026</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D121" s="1" t="n">
+      <c r="D122" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="E121" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
+      <c r="E122" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
         <v>2.6</v>
       </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>S 1377-2026</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D122" s="1" t="n">
+      <c r="D123" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="E122" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
+      <c r="E123" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
         <v>7</v>
       </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="2" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>46281</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45271</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45677</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45770</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46064</v>
+        <v>44860</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>12.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1747,49 +1747,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46120</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,42 +1859,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44860</v>
+        <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1957,49 +1957,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854</v>
+        <v>46064</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2029,17 +2029,17 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2069,42 +2069,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45414</v>
+        <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2134,17 +2134,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2174,35 +2174,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
         <v>45056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2384,35 +2384,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44833</v>
+        <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3650,14 +3650,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44596</v>
+        <v>45195</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3730,7 +3730,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45674</v>
+        <v>45243</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45068</v>
+        <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3942,14 +3942,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45551</v>
+        <v>45110</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>45196</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45110</v>
+        <v>44833</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45306</v>
+        <v>45622</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45233</v>
+        <v>45180</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44831</v>
+        <v>45068</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45148</v>
+        <v>45551</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45110</v>
+        <v>45491</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45235</v>
+        <v>45180</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45000</v>
+        <v>45235</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45300</v>
+        <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45674</v>
+        <v>45365</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46064</v>
+        <v>44831</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4881,7 +4881,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46071</v>
+        <v>45117</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46071</v>
+        <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44824</v>
+        <v>45148</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45180</v>
+        <v>44862</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45833</v>
+        <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5202,8 +5202,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5246,7 +5251,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5260,10 +5265,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45728</v>
+        <v>45566</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5276,7 +5281,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5319,7 +5324,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5333,10 +5338,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45365</v>
+        <v>45728</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5349,7 +5354,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5392,7 +5397,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5406,10 +5411,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45629</v>
+        <v>44824</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5422,7 +5427,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5465,7 +5470,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,10 +5484,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45817</v>
+        <v>45148</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5495,7 +5500,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5538,7 +5543,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5552,10 +5557,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44862</v>
+        <v>44911</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5567,8 +5572,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5611,7 +5621,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5625,10 +5635,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45512</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5641,7 +5651,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5684,7 +5694,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5698,10 +5708,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45126</v>
+        <v>45817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5713,13 +5723,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>12.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5762,7 +5767,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5776,10 +5781,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45148</v>
+        <v>45629</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5792,7 +5797,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5852,7 +5857,7 @@
         <v>45972</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5908,7 +5913,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45947</v>
+        <v>45233</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5938,7 +5943,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5981,7 +5986,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5995,10 +6000,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45993</v>
+        <v>45174</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,13 +6015,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45996</v>
+        <v>45299</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6161,8 +6161,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6205,7 +6210,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46136</v>
+        <v>45996</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6235,7 +6240,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6278,7 +6283,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6292,10 +6297,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45866</v>
+        <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6308,7 +6313,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6351,7 +6356,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45033</v>
+        <v>45889</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6381,7 +6386,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6424,7 +6429,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45889</v>
+        <v>45674</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6454,7 +6459,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6497,7 +6502,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6511,10 +6516,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45937</v>
+        <v>45306</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6527,7 +6532,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6570,7 +6575,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6584,10 +6589,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46184</v>
+        <v>44804</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6600,7 +6605,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6643,7 +6648,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6657,10 +6662,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46183</v>
+        <v>45937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6673,7 +6678,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>15.6</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6716,7 +6721,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6730,10 +6735,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45104</v>
+        <v>45674</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6746,7 +6751,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6789,7 +6794,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6803,10 +6808,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45384</v>
+        <v>45866</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6819,7 +6824,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6862,7 +6867,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6876,10 +6881,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45622</v>
+        <v>45033</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6892,7 +6897,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6935,7 +6940,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6949,10 +6954,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46195</v>
+        <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6965,7 +6970,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7008,7 +7013,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7022,10 +7027,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45300</v>
+        <v>45148</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7038,7 +7043,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7081,7 +7086,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7095,10 +7100,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44911</v>
+        <v>45217</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7110,13 +7115,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7159,7 +7159,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46230</v>
+        <v>46183</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>15.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7232,7 +7232,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44804</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7319,10 +7319,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46230</v>
+        <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45566</v>
+        <v>44993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45299</v>
+        <v>46195</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45243</v>
+        <v>46071</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7597,7 +7597,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44993</v>
+        <v>46071</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7670,7 +7670,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7684,10 +7684,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45217</v>
+        <v>45833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46290</v>
+        <v>45000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45196</v>
+        <v>44494</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7889,7 +7889,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7903,10 +7903,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46290</v>
+        <v>45357</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7962,7 +7962,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45566</v>
+        <v>45127</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45148</v>
+        <v>45415</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8108,7 +8108,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41398-2026</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8122,10 +8122,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46300</v>
+        <v>46136</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8181,7 +8181,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44494</v>
+        <v>45947</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8254,7 +8254,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45117</v>
+        <v>45512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8327,7 +8327,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45127</v>
+        <v>45384</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45174</v>
+        <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45208</v>
+        <v>45566</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45110</v>
+        <v>45104</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45180</v>
+        <v>46230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45357</v>
+        <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8765,7 +8765,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45174</v>
+        <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8838,7 +8838,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45415</v>
+        <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8911,7 +8911,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45195</v>
+        <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 41398-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45491</v>
+        <v>46300</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24688-2025</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45798</v>
+        <v>45056</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1204,592 +1204,593 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Hålnunneört</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 38164-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 24688-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45798</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Mindre flugsnappare</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 38164-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J8" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S 4458-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45271</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S 4458-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45271</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Lundbräsma
 Lömsk flugsvamp</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 4458-2023 artfynd.xlsx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 4458-2023 karta.png", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 4458-2023 georefererad karta.tif", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 4458-2023 FSC-klagomål.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 4458-2023 FSC-klagomål mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 4458-2023 tillsynsbegäran.docx", "S 4458-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 4458-2023 tillsynsbegäran mail.docx", "S 4458-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>S 168-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45677</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 168-2025 artfynd.xlsx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 168-2025 karta.png", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 168-2025 georefererad karta.tif", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 168-2025 FSC-klagomål.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 168-2025 FSC-klagomål mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 168-2025 tillsynsbegäran.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 168-2025 tillsynsbegäran mail.docx", "S 168-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 168-2025 prioriterade fågelarter.docx", "S 168-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>S 1328-2025</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>27.2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Luddfingerört</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/S 1328-2025 artfynd.xlsx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/S 1328-2025 karta.png", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/S 1328-2025 georefererad karta.tif", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/S 1328-2025 FSC-klagomål.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/S 1328-2025 FSC-klagomål mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/S 1328-2025 tillsynsbegäran.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/S 1328-2025 tillsynsbegäran mail.docx", "S 1328-2025")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/S 1328-2025 prioriterade fågelarter.docx", "S 1328-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50118-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44860</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,10 +1804,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45414</v>
+        <v>44860</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1819,7 +1820,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1852,49 +1853,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45222</v>
+        <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,14 +1928,14 @@
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1948,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,42 +1965,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2013,10 +2014,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46064</v>
+        <v>45414</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2029,16 +2030,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2053,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2069,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2118,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46120</v>
+        <v>45854</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2134,16 +2135,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2158,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2174,42 +2175,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2223,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45056</v>
+        <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2239,7 +2240,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2275,46 +2276,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2328,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45854</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2344,13 +2345,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2384,35 +2385,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2436,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2650,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2860,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2965,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3074,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3183,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3292,7 +3293,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3365,7 +3366,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3438,7 +3439,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3511,7 +3512,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3567,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3581,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45110</v>
+        <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3597,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3640,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3650,14 +3651,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45195</v>
+        <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3670,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3713,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3730,7 +3731,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3743,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3786,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3800,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45243</v>
+        <v>45674</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3816,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3859,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3873,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44596</v>
+        <v>45068</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3889,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3932,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3942,14 +3943,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45110</v>
+        <v>45551</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3962,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4005,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4019,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45196</v>
+        <v>45110</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4035,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4078,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4092,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44833</v>
+        <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4108,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4151,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45622</v>
+        <v>45306</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4181,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4224,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4238,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45180</v>
+        <v>45233</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4254,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4297,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4311,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45068</v>
+        <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4327,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4370,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4380,14 +4381,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45551</v>
+        <v>45148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4400,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4443,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45491</v>
+        <v>45110</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4516,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4530,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45180</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4546,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4606,7 +4607,7 @@
         <v>45235</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4662,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4676,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45110</v>
+        <v>45674</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4692,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4735,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4749,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45365</v>
+        <v>44824</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4765,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4808,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4822,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44831</v>
+        <v>45180</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4838,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4881,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4895,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45117</v>
+        <v>45629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4911,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4954,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4968,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45300</v>
+        <v>45817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>12.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5027,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5041,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45148</v>
+        <v>45365</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5117,7 +5118,7 @@
         <v>44862</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5190,7 +5191,7 @@
         <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5251,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5265,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45566</v>
+        <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5281,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5324,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5338,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45728</v>
+        <v>45033</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5354,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5397,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5411,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44824</v>
+        <v>45728</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5427,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5470,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5484,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45148</v>
+        <v>45104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5500,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5543,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5557,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44911</v>
+        <v>45384</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,13 +5573,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5621,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5635,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>45622</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5694,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5708,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45817</v>
+        <v>45972</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>12.7</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5767,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5781,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45629</v>
+        <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5797,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5840,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5854,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5869,8 +5865,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5913,7 +5914,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5927,10 +5928,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45233</v>
+        <v>45300</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5943,7 +5944,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5986,7 +5987,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6000,10 +6001,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45174</v>
+        <v>45947</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6016,7 +6017,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6059,7 +6060,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6073,10 +6074,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45299</v>
+        <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6089,7 +6090,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6132,7 +6133,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6146,10 +6147,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6161,13 +6162,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6210,7 +6206,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6224,10 +6220,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45996</v>
+        <v>45866</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6236,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6283,7 +6279,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6297,10 +6293,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45996</v>
+        <v>46136</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6309,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6356,7 +6352,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6370,10 +6366,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45889</v>
+        <v>46064</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6382,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6429,7 +6425,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6443,10 +6439,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45674</v>
+        <v>46071</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6455,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6502,7 +6498,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6516,10 +6512,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45306</v>
+        <v>46071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6528,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6575,7 +6571,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6589,10 +6585,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44804</v>
+        <v>44911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6604,8 +6600,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6648,7 +6649,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6662,10 +6663,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45937</v>
+        <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6679,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6721,7 +6722,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6735,10 +6736,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45674</v>
+        <v>44804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6752,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6794,7 +6795,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6808,10 +6809,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45866</v>
+        <v>45889</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6825,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6867,7 +6868,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6881,10 +6882,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45033</v>
+        <v>45566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6898,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6940,7 +6941,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6954,10 +6955,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45174</v>
+        <v>45299</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6971,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7013,7 +7014,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7027,10 +7028,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45148</v>
+        <v>45937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7044,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7086,7 +7087,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7100,10 +7101,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45217</v>
+        <v>45243</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7117,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7159,7 +7160,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7173,10 +7174,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46183</v>
+        <v>44993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7190,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>15.6</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7232,7 +7233,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7246,10 +7247,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7263,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7305,7 +7306,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7319,10 +7320,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46064</v>
+        <v>46184</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7336,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7378,7 +7379,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44993</v>
+        <v>45196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7409,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7451,7 +7452,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7465,10 +7466,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46195</v>
+        <v>45566</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7482,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7524,7 +7525,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7538,10 +7539,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46071</v>
+        <v>46195</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7555,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7597,7 +7598,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7611,10 +7612,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46071</v>
+        <v>45148</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7628,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7670,7 +7671,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7684,10 +7685,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45833</v>
+        <v>44494</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7701,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7743,7 +7744,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7757,10 +7758,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45000</v>
+        <v>45117</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7774,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7816,7 +7817,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7830,10 +7831,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44494</v>
+        <v>45127</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7847,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7889,7 +7890,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7903,10 +7904,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45357</v>
+        <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7920,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7962,7 +7963,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45127</v>
+        <v>45208</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7992,7 +7993,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8035,7 +8036,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8049,10 +8050,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45415</v>
+        <v>45110</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8065,7 +8066,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8108,7 +8109,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8122,10 +8123,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46136</v>
+        <v>46230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8138,7 +8139,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8181,7 +8182,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8195,10 +8196,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45947</v>
+        <v>46230</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8211,7 +8212,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8254,7 +8255,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8268,10 +8269,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45512</v>
+        <v>45180</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8284,7 +8285,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8327,7 +8328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8341,10 +8342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45384</v>
+        <v>45357</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8357,7 +8358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8400,7 +8401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8414,10 +8415,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45208</v>
+        <v>45174</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8430,7 +8431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8473,7 +8474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8487,10 +8488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45566</v>
+        <v>45415</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8503,7 +8504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8546,7 +8547,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8556,14 +8557,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45104</v>
+        <v>45195</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8576,7 +8577,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8619,7 +8620,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8633,10 +8634,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46230</v>
+        <v>45491</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8649,7 +8650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8692,7 +8693,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8706,10 +8707,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46230</v>
+        <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8722,7 +8723,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8765,7 +8766,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8779,10 +8780,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45300</v>
+        <v>46290</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8795,7 +8796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8855,7 +8856,7 @@
         <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8911,7 +8912,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 41398-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8925,10 +8926,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46290</v>
+        <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8941,7 +8942,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8984,7 +8985,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41398-2026</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8998,10 +8999,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46300</v>
+        <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9014,7 +9015,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9074,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9147,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9220,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9293,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9366,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9439,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9512,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9585,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9658,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9731,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9804,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9877,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9950,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10023,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10096,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10169,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10242,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10315,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45056</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46281</v>
+        <v>45798</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1310,154 +1310,154 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 38164-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 24688-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45798</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Mindre flugsnappare</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44860</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1853,49 +1853,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46120</v>
+        <v>44860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1958,49 +1958,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45414</v>
+        <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2070,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45854</v>
+        <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,17 +2135,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2175,42 +2175,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46064</v>
+        <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>46064</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2345,17 +2345,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2385,35 +2385,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64621-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44511</v>
+        <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44594</v>
+        <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44509</v>
+        <v>44596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30978-2022</t>
+          <t>A 64621-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44768</v>
+        <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 30978-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44833</v>
+        <v>44768</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,7 +3658,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44596</v>
+        <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45674</v>
+        <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45068</v>
+        <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45551</v>
+        <v>45127</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45110</v>
+        <v>45235</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,7 +4096,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45306</v>
+        <v>45415</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45233</v>
+        <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44831</v>
+        <v>45196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45148</v>
+        <v>45384</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45110</v>
+        <v>45365</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>45208</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45235</v>
+        <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45674</v>
+        <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44824</v>
+        <v>45148</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45180</v>
+        <v>45104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45629</v>
+        <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45817</v>
+        <v>45622</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.7</v>
+        <v>6.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45365</v>
+        <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44862</v>
+        <v>45126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5130,8 +5130,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45126</v>
+        <v>45566</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5203,13 +5208,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45148</v>
+        <v>45491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45033</v>
+        <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45728</v>
+        <v>44911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5427,8 +5427,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5476,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45104</v>
+        <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5506,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5549,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45384</v>
+        <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5579,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5622,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45622</v>
+        <v>45300</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5652,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5695,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5709,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45972</v>
+        <v>45728</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5725,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5768,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45512</v>
+        <v>45233</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5798,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5841,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5855,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45993</v>
+        <v>45299</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5865,13 +5870,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5914,7 +5914,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45300</v>
+        <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5987,7 +5987,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45947</v>
+        <v>45674</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6060,7 +6060,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45996</v>
+        <v>45674</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45996</v>
+        <v>45033</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6206,7 +6206,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6220,10 +6220,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45866</v>
+        <v>45306</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46136</v>
+        <v>45972</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46064</v>
+        <v>44804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46071</v>
+        <v>45174</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6512,10 +6512,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46071</v>
+        <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44911</v>
+        <v>45217</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6600,13 +6600,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45833</v>
+        <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6679,7 +6674,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6722,7 +6717,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6732,14 +6727,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44804</v>
+        <v>45195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6752,7 +6747,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6795,7 +6790,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6809,10 +6804,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45889</v>
+        <v>45243</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6825,7 +6820,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6868,7 +6863,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6882,10 +6877,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45566</v>
+        <v>45817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6898,7 +6893,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>12.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6941,7 +6936,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6955,10 +6950,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45299</v>
+        <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6971,7 +6966,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7014,7 +7009,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7028,10 +7023,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45937</v>
+        <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7044,7 +7039,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7087,7 +7082,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7101,10 +7096,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45243</v>
+        <v>45180</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7117,7 +7112,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7160,7 +7155,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7174,10 +7169,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44993</v>
+        <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7190,7 +7185,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7233,7 +7228,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7243,14 +7238,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45217</v>
+        <v>45551</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7263,7 +7258,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7306,7 +7301,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7320,10 +7315,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46184</v>
+        <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,8 +7330,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7379,7 +7379,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45196</v>
+        <v>45996</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45566</v>
+        <v>44993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46195</v>
+        <v>45996</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7598,7 +7598,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45148</v>
+        <v>46136</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7671,7 +7671,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7685,10 +7685,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44494</v>
+        <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7744,7 +7744,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45117</v>
+        <v>45512</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45127</v>
+        <v>45866</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7890,7 +7890,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45174</v>
+        <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45208</v>
+        <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8036,7 +8036,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45110</v>
+        <v>46064</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8109,7 +8109,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46230</v>
+        <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8182,7 +8182,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46230</v>
+        <v>46071</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8255,7 +8255,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8269,10 +8269,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45180</v>
+        <v>45833</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45357</v>
+        <v>45889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8401,7 +8401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8415,10 +8415,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45174</v>
+        <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45415</v>
+        <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8557,14 +8557,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45195</v>
+        <v>46195</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45491</v>
+        <v>46230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45300</v>
+        <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8783,7 +8783,7 @@
         <v>46290</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8839,7 +8839,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8856,7 +8856,7 @@
         <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8929,7 +8929,7 @@
         <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45056</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45798</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46281</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46064</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44768</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45127</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45235</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45415</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45384</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45365</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45208</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45148</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45622</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45566</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45300</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45728</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45233</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45299</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45674</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45674</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45033</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45306</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45972</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45174</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45217</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45243</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45180</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45551</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45996</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45996</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46136</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45512</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45866</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>46064</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46071</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45833</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>46195</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>46230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>46290</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45056</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>45798</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46281</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>45854</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46064</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44594</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44509</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44511</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44768</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45180</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45127</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45235</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45415</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45384</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45365</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45208</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45148</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45104</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45622</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45566</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44824</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45300</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45728</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45233</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45299</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45674</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45674</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45033</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45306</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45972</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44804</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45174</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45148</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45217</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45110</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45243</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45180</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45551</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45996</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45996</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46136</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45947</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45512</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45866</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>46064</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46071</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46071</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45833</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>46195</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>46230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>46230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>46290</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>46290</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 20426-2023</t>
+          <t>A 24688-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45056</v>
+        <v>45798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1204,260 +1204,260 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 38164-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20426-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45056</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Hålnunneört</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 24688-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45798</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Mindre flugsnappare</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 24688-2025 artfynd.xlsx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 24688-2025 karta.png", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 24688-2025 georefererad karta.tif", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 24688-2025 FSC-klagomål.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 24688-2025 FSC-klagomål mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 24688-2025 tillsynsbegäran.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 24688-2025 tillsynsbegäran mail.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 24688-2025 prioriterade fågelarter.docx", "A 24688-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 38164-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45414</v>
+        <v>46064</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1860,42 +1860,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44860</v>
+        <v>46120</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,17 +1925,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12.8</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1958,49 +1958,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45222</v>
+        <v>45854</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2070,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46120</v>
+        <v>44860</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,16 +2135,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2168,49 +2168,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46064</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2385,35 +2385,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5320-2022</t>
+          <t>A 64621-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44594</v>
+        <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63681-2021</t>
+          <t>A 5320-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44509</v>
+        <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5816-2022</t>
+          <t>A 63681-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44596</v>
+        <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64621-2021</t>
+          <t>A 30978-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44511</v>
+        <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30978-2022</t>
+          <t>A 42963-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44768</v>
+        <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5779-2022</t>
+          <t>A 5816-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,7 +3658,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 42963-2022</t>
+          <t>A 5779-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44833</v>
+        <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45180</v>
+        <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45357</v>
+        <v>45127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45127</v>
+        <v>45174</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45235</v>
+        <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45110</v>
+        <v>45208</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45415</v>
+        <v>45110</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44831</v>
+        <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45196</v>
+        <v>46184</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45384</v>
+        <v>45180</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45365</v>
+        <v>45357</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45208</v>
+        <v>45728</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42909-2024</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45566</v>
+        <v>45174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45117</v>
+        <v>46195</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45148</v>
+        <v>45415</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45104</v>
+        <v>45195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45300</v>
+        <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45622</v>
+        <v>45491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44862</v>
+        <v>45993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5057,8 +5057,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45126</v>
+        <v>45300</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5130,13 +5135,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45566</v>
+        <v>45996</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45491</v>
+        <v>45996</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44824</v>
+        <v>46230</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44911</v>
+        <v>45551</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5427,13 +5427,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5476,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5493,7 +5488,7 @@
         <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5506,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5549,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45148</v>
+        <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5579,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5622,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45300</v>
+        <v>46230</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5652,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5695,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45728</v>
+        <v>45866</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5725,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5768,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45233</v>
+        <v>45306</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5841,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45299</v>
+        <v>45629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5871,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5914,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5928,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45174</v>
+        <v>45817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5944,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>12.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5987,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6001,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45674</v>
+        <v>46064</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6017,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6060,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6074,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45674</v>
+        <v>46071</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6090,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6133,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6147,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45033</v>
+        <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6163,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6206,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6220,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45306</v>
+        <v>45233</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6293,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45972</v>
+        <v>46290</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6309,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6352,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6366,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44804</v>
+        <v>45833</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6382,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6425,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6439,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45174</v>
+        <v>46290</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6455,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6498,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6512,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45148</v>
+        <v>44831</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6528,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6571,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 41398-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6585,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45217</v>
+        <v>46300</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6601,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6644,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6658,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>45148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6674,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6717,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6727,14 +6722,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45195</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6747,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6790,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6804,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45243</v>
+        <v>45235</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6820,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6863,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6877,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45817</v>
+        <v>46183</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6893,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6936,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6950,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45629</v>
+        <v>45512</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6966,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7009,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7023,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45110</v>
+        <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7039,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7082,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7096,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45180</v>
+        <v>45947</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7112,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7155,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7169,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45068</v>
+        <v>45674</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7185,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7228,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7238,14 +7233,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45551</v>
+        <v>46136</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7258,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7301,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7315,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45993</v>
+        <v>44824</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7328,11 +7323,6 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7379,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7393,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45996</v>
+        <v>45180</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7409,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7452,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7466,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44993</v>
+        <v>45889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7482,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7525,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7539,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45996</v>
+        <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7555,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7598,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7612,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46136</v>
+        <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7628,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7671,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7685,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45947</v>
+        <v>45126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,8 +7690,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7744,7 +7739,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7758,10 +7753,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45512</v>
+        <v>45148</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7774,7 +7769,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7817,7 +7812,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7831,10 +7826,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45866</v>
+        <v>45937</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7847,7 +7842,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7890,7 +7885,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7904,10 +7899,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45000</v>
+        <v>45033</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7920,7 +7915,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7963,7 +7958,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7977,10 +7972,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44494</v>
+        <v>45104</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7993,7 +7988,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8036,7 +8031,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8050,10 +8045,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46064</v>
+        <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8066,7 +8061,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8109,7 +8104,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8123,10 +8118,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46071</v>
+        <v>45622</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8139,7 +8134,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8182,7 +8177,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8196,10 +8191,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46071</v>
+        <v>45300</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8212,7 +8207,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8255,7 +8250,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8269,10 +8264,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45833</v>
+        <v>44911</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8284,8 +8279,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45889</v>
+        <v>44804</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8401,7 +8401,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 42909-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8415,10 +8415,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45937</v>
+        <v>45566</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46184</v>
+        <v>45299</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46195</v>
+        <v>45243</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46230</v>
+        <v>44993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46230</v>
+        <v>45217</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46290</v>
+        <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8839,7 +8839,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46290</v>
+        <v>45566</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 41398-2026</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46300</v>
+        <v>45148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8985,7 +8985,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46183</v>
+        <v>44494</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>15.6</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>46281</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8362-2026</t>
+          <t>A 50118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46064</v>
+        <v>44860</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>12.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1853,49 +1853,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17522-2026</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46120</v>
+        <v>45414</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1965,42 +1965,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Sminkrot</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35397-2025</t>
+          <t>A 52972-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45854</v>
+        <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2070,42 +2070,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 8362-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44860</v>
+        <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,17 +2135,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>12.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2168,49 +2168,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 8362-2026 artfynd.xlsx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 8362-2026 karta.png", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 8362-2026 georefererad karta.tif", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 8362-2026 FSC-klagomål.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 50118-2022 FSC-klagomål mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 8362-2026 FSC-klagomål mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 50118-2022 tillsynsbegäran.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 8362-2026 tillsynsbegäran.docx", "A 8362-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 50118-2022 tillsynsbegäran mail.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 8362-2026 tillsynsbegäran mail.docx", "A 8362-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17396-2024</t>
+          <t>A 17522-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45414</v>
+        <v>46120</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2240,17 +2240,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Safsa</t>
+          <t>Sminkrot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17522-2026 artfynd.xlsx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17522-2026 karta.png", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17522-2026 georefererad karta.tif", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomål.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17522-2026 FSC-klagomål.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17396-2024 FSC-klagomål mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 17522-2026 FSC-klagomål mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17396-2024 tillsynsbegäran.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 17522-2026 tillsynsbegäran.docx", "A 17522-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17396-2024 tillsynsbegäran mail.docx", "A 17396-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 17522-2026 tillsynsbegäran mail.docx", "A 17522-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52972-2023</t>
+          <t>A 35397-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>45854</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2385,35 +2385,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 52972-2023 artfynd.xlsx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 35397-2025 artfynd.xlsx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 52972-2023 karta.png", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 35397-2025 karta.png", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 52972-2023 georefererad karta.tif", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 35397-2025 georefererad karta.tif", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 52972-2023 FSC-klagomål.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 35397-2025 FSC-klagomål.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 52972-2023 FSC-klagomål mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 35397-2025 FSC-klagomål mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 52972-2023 tillsynsbegäran.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 35397-2025 tillsynsbegäran.docx", "A 35397-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 52972-2023 tillsynsbegäran mail.docx", "A 52972-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 35397-2025 tillsynsbegäran mail.docx", "A 35397-2025")</f>
         <v/>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45106</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45770</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>46147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44509</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44833</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31649-2023</t>
+          <t>A 47315-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45117</v>
+        <v>45196</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33255-2023</t>
+          <t>A 10275-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45127</v>
+        <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41254-2023</t>
+          <t>A 36086-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45174</v>
+        <v>45866</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2448-2025</t>
+          <t>A 31649-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45674</v>
+        <v>45117</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48738-2023</t>
+          <t>A 745-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45208</v>
+        <v>45300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30075-2023</t>
+          <t>A 49831-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45110</v>
+        <v>44862</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21980-2023</t>
+          <t>A 34216-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45068</v>
+        <v>45126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4254,8 +4254,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4303,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26765-2026</t>
+          <t>A 42912-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4317,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46184</v>
+        <v>45566</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4333,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4376,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42333-2023</t>
+          <t>A 11861-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4390,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45180</v>
+        <v>45728</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4406,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4449,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9006-2024</t>
+          <t>A 61701-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4463,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45357</v>
+        <v>44911</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,8 +4478,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4527,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11861-2025</t>
+          <t>A 30112-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4541,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45728</v>
+        <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4557,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4600,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41253-2023</t>
+          <t>A 27965-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4614,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45174</v>
+        <v>45817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4630,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>12.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4673,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28129-2026</t>
+          <t>A 57181-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4687,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46195</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4703,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4746,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17517-2024</t>
+          <t>A 55762-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4760,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45415</v>
+        <v>45972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4776,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4819,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46733-2023</t>
+          <t>A 576-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4829,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45195</v>
+        <v>45299</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4849,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4892,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55762-2025</t>
+          <t>A 8366-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4906,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45972</v>
+        <v>46064</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4922,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4965,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30407-2024</t>
+          <t>A 60055-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4979,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45491</v>
+        <v>45993</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,8 +4994,13 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5043,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60055-2025</t>
+          <t>A 60698-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5057,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5057,13 +5072,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5116,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 745-2024</t>
+          <t>A 60696-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5130,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45300</v>
+        <v>45996</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5146,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5189,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60698-2025</t>
+          <t>A 9508-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5203,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45996</v>
+        <v>46071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5219,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5262,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60696-2025</t>
+          <t>A 9509-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5276,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45996</v>
+        <v>46071</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5292,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5335,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31810-2026</t>
+          <t>A 2453-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5349,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46230</v>
+        <v>45674</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5365,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5408,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39455-2024</t>
+          <t>A 2448-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5408,14 +5418,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45551</v>
+        <v>45674</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5438,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5481,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30089-2023</t>
+          <t>A 17253-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5495,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45110</v>
+        <v>45033</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5511,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5554,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30112-2023</t>
+          <t>A 31404-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5568,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45110</v>
+        <v>45833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5584,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5627,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31815-2026</t>
+          <t>A 41253-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5641,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46230</v>
+        <v>45174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5657,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5700,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36086-2025</t>
+          <t>A 35804-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5714,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45866</v>
+        <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5730,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5773,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1566-2024</t>
+          <t>A 52307-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5787,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45306</v>
+        <v>45217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5803,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5846,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57181-2024</t>
+          <t>A 30089-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5860,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45629</v>
+        <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5909,7 +5919,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27965-2025</t>
+          <t>A 46733-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5919,14 +5929,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45817</v>
+        <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5949,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5992,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8366-2026</t>
+          <t>A 56360-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +6006,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46064</v>
+        <v>45243</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6022,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6065,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9508-2026</t>
+          <t>A 30075-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6079,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46071</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6095,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6138,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9509-2026</t>
+          <t>A 43276-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6152,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46071</v>
+        <v>45180</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6168,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6211,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56056-2023</t>
+          <t>A 21980-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6225,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45233</v>
+        <v>45068</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6241,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6284,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40177-2026</t>
+          <t>A 39455-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6284,14 +6294,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46290</v>
+        <v>45551</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6314,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6357,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31404-2025</t>
+          <t>A 42333-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6371,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45833</v>
+        <v>45180</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6387,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6430,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40214-2026</t>
+          <t>A 54689-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6444,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46290</v>
+        <v>45235</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6460,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6503,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42748-2022</t>
+          <t>A 30101-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6517,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44831</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6533,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6576,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41398-2026</t>
+          <t>A 42748-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6590,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46300</v>
+        <v>44831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6606,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6649,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35804-2023</t>
+          <t>A 20136-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6663,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45148</v>
+        <v>46136</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6679,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6722,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30101-2023</t>
+          <t>A 51078-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6736,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45110</v>
+        <v>45947</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6752,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6795,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54689-2023</t>
+          <t>A 32272-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6809,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45235</v>
+        <v>45512</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6825,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6868,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26477-2026</t>
+          <t>A 35802-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6882,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46183</v>
+        <v>45148</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6898,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>15.6</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6941,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32272-2024</t>
+          <t>A 40719-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6955,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45512</v>
+        <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6971,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7014,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12721-2023</t>
+          <t>A 35798-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7028,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45000</v>
+        <v>45148</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7044,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7087,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51078-2025</t>
+          <t>A 39284-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7101,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45947</v>
+        <v>45889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7117,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7160,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2453-2025</t>
+          <t>A 48974-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7174,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45674</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7190,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7233,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20136-2026</t>
+          <t>A 56056-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7247,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46136</v>
+        <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7263,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7306,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40719-2022</t>
+          <t>A 41254-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7320,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44824</v>
+        <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7336,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7379,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43276-2023</t>
+          <t>A 1566-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7393,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45180</v>
+        <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7409,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7452,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39284-2025</t>
+          <t>A 36421-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7466,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45889</v>
+        <v>44804</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7482,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7525,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10275-2024</t>
+          <t>A 26765-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7539,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45365</v>
+        <v>46184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7555,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7598,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49831-2022</t>
+          <t>A 28129-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7612,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44862</v>
+        <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7628,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7671,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34216-2023</t>
+          <t>A 11454-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7685,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45126</v>
+        <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7690,13 +7700,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7739,7 +7744,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35798-2023</t>
+          <t>A 12721-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7753,10 +7758,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45148</v>
+        <v>45000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7769,7 +7774,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7812,7 +7817,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48974-2025</t>
+          <t>A 31810-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7826,10 +7831,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45937</v>
+        <v>46230</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7842,7 +7847,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7885,7 +7890,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17253-2023</t>
+          <t>A 31815-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7899,10 +7904,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45033</v>
+        <v>46230</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7915,7 +7920,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7958,7 +7963,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28870-2023</t>
+          <t>A 59949-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7972,10 +7977,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45104</v>
+        <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7988,7 +7993,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8031,7 +8036,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12685-2024</t>
+          <t>A 9006-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8045,10 +8050,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45384</v>
+        <v>45357</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8061,7 +8066,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8104,7 +8109,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55901-2024</t>
+          <t>A 33255-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8118,10 +8123,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45622</v>
+        <v>45127</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8134,7 +8139,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8177,7 +8182,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 814-2024</t>
+          <t>A 17517-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8191,10 +8196,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45300</v>
+        <v>45415</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8207,7 +8212,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8250,7 +8255,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61701-2022</t>
+          <t>A 12685-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8264,10 +8269,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44911</v>
+        <v>45384</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8279,13 +8284,8 @@
           <t>BROMÖLLA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36421-2022</t>
+          <t>A 48738-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44804</v>
+        <v>45208</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8418,7 +8418,7 @@
         <v>45566</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 576-2024</t>
+          <t>A 28870-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45299</v>
+        <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56360-2023</t>
+          <t>A 814-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45243</v>
+        <v>45300</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11454-2023</t>
+          <t>A 40214-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44993</v>
+        <v>46290</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52307-2023</t>
+          <t>A 40177-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45217</v>
+        <v>46290</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8766,7 +8766,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47315-2023</t>
+          <t>A 55901-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45196</v>
+        <v>45622</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8839,7 +8839,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42912-2024</t>
+          <t>A 30407-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45566</v>
+        <v>45491</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 35802-2023</t>
+          <t>A 41398-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45148</v>
+        <v>46300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8985,7 +8985,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59949-2021</t>
+          <t>A 26477-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44494</v>
+        <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>15.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
         <v>45677</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45677</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44796</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45440</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45677</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45106</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45230</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46149</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt BROMÖLLA.xlsx
+++ b/Översikt BROMÖLLA.xlsx
@@ -601,7 +601,7 @@
         <v>44526</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>46127</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45561</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>45677</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>45798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38164-2026</t>
+          <t>A 20426-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46281</v>
+        <v>45056</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1278,17 +1278,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1318,146 +1318,146 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Bokvårtlav
+Hålnunneört</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 38164-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BROMÖLLA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 38164-2026 artfynd.xlsx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 38164-2026 karta.png", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 38164-2026 georefererad karta.tif", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 38164-2026 FSC-klagomål.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 38164-2026 FSC-klagomål mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 38164-2026 tillsynsbegäran.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 38164-2026 tillsynsbegäran mail.docx", "A 38164-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1272/fåglar/A 38164-2026 prioriterade fågelarter.docx", "A 38164-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20426-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45056</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BROMÖLLA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Hålnunneört</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 20426-2023 artfynd.xlsx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 20426-2023 karta.png", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 20426-2023 georefererad karta.tif", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 20426-2023 FSC-klagomål.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomålsmail/A 20426-2023 FSC-klagomål mail.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsyn/A 20426-2023 tillsynsbegäran.docx", "A 20426-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/tillsynsmail/A 20426-2023 tillsynsbegäran mail.docx", "A 20426-2023")</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         <v>45271</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>45677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45770</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50118-2022</t>
+          <t>A 17396-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44860</v>
+        <v>45414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1853,49 +1853,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Safsa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 50118-2022 artfynd.xlsx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/artfynd/A 17396-2024 artfynd.xlsx", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 50118-2022 karta.png", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor/A 17396-2024 karta.png", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 50118-2022 georefererad karta.tif", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/kartor_geotiff/A 17396-2024 georefererad karta.tif", "A 17396-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 50118-2022 FSC-klagomål.docx", "A 50118-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1272/klagomål/A 17396-2024 FSC-klagomå